--- a/4. JADWAL DAN KALDIK 2026-2027.xlsx
+++ b/4. JADWAL DAN KALDIK 2026-2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MABAIZ\Persiapan RKT 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07BB0AD-B292-4DB7-B3B2-F44372C17878}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D0D4D0-3A39-4FDE-BFE4-405A5BB3F589}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JADWAL DINIYAH (2)" sheetId="5" r:id="rId1"/>
@@ -1184,7 +1184,7 @@
     <t>27 - (21)</t>
   </si>
   <si>
-    <t>Bagi rapot + Libur Semester</t>
+    <t>Bagi rapot</t>
   </si>
 </sst>
 </file>
@@ -2845,7 +2845,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="555">
+  <cellXfs count="559">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4280,31 +4280,67 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="65" fillId="11" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="51" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="51" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="51" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="51" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="51" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="55" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="11" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="51" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="51" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="51" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -4316,9 +4352,6 @@
     <xf numFmtId="0" fontId="66" fillId="48" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="52" fillId="15" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4328,97 +4361,64 @@
     <xf numFmtId="0" fontId="3" fillId="49" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="15" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="66" fillId="48" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="57" fillId="42" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="37" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="37" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="37" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="42" fillId="37" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="42" fillId="37" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="42" fillId="37" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -4431,146 +4431,162 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="37" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="44" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="38" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="34" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="37" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="44" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="38" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="34" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="49" fillId="23" borderId="56" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="23" borderId="56" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" xfId="2" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4924,16 +4940,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:17" ht="30">
-      <c r="D1" s="462" t="s">
+      <c r="D1" s="468" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="462"/>
-      <c r="F1" s="462"/>
-      <c r="G1" s="462"/>
-      <c r="H1" s="462"/>
-      <c r="I1" s="462"/>
-      <c r="J1" s="462"/>
-      <c r="K1" s="462"/>
+      <c r="E1" s="468"/>
+      <c r="F1" s="468"/>
+      <c r="G1" s="468"/>
+      <c r="H1" s="468"/>
+      <c r="I1" s="468"/>
+      <c r="J1" s="468"/>
+      <c r="K1" s="468"/>
     </row>
     <row r="3" spans="4:17" s="427" customFormat="1" ht="36.75" customHeight="1">
       <c r="D3" s="429" t="s">
@@ -4965,7 +4981,7 @@
       <c r="Q3" s="463"/>
     </row>
     <row r="4" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D4" s="465">
+      <c r="D4" s="469">
         <v>1</v>
       </c>
       <c r="E4" s="431" t="s">
@@ -4993,7 +5009,7 @@
       <c r="P4" s="433"/>
     </row>
     <row r="5" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D5" s="466"/>
+      <c r="D5" s="470"/>
       <c r="E5" s="434" t="s">
         <v>15</v>
       </c>
@@ -5009,7 +5025,7 @@
       <c r="P5" s="433"/>
     </row>
     <row r="6" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D6" s="466"/>
+      <c r="D6" s="470"/>
       <c r="E6" s="435" t="s">
         <v>17</v>
       </c>
@@ -5035,7 +5051,7 @@
       <c r="P6" s="433"/>
     </row>
     <row r="7" spans="4:17" ht="24.95" hidden="1" customHeight="1">
-      <c r="D7" s="466"/>
+      <c r="D7" s="470"/>
       <c r="E7" s="435"/>
       <c r="F7" s="436"/>
       <c r="G7" s="436"/>
@@ -5047,7 +5063,7 @@
       <c r="P7" s="433"/>
     </row>
     <row r="8" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D8" s="466"/>
+      <c r="D8" s="470"/>
       <c r="E8" s="434" t="s">
         <v>19</v>
       </c>
@@ -5063,7 +5079,7 @@
       <c r="P8" s="433"/>
     </row>
     <row r="9" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D9" s="467">
+      <c r="D9" s="462">
         <v>2</v>
       </c>
       <c r="E9" s="437" t="s">
@@ -5091,7 +5107,7 @@
       <c r="P9" s="433"/>
     </row>
     <row r="10" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D10" s="467"/>
+      <c r="D10" s="462"/>
       <c r="E10" s="434" t="s">
         <v>15</v>
       </c>
@@ -5107,7 +5123,7 @@
       <c r="P10" s="433"/>
     </row>
     <row r="11" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D11" s="467"/>
+      <c r="D11" s="462"/>
       <c r="E11" s="437" t="s">
         <v>17</v>
       </c>
@@ -5134,7 +5150,7 @@
       <c r="Q11" s="463"/>
     </row>
     <row r="12" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D12" s="467"/>
+      <c r="D12" s="462"/>
       <c r="E12" s="434" t="s">
         <v>19</v>
       </c>
@@ -5151,7 +5167,7 @@
       <c r="Q12" s="430"/>
     </row>
     <row r="13" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D13" s="467">
+      <c r="D13" s="462">
         <v>3</v>
       </c>
       <c r="E13" s="437" t="s">
@@ -5179,23 +5195,23 @@
       <c r="P13" s="439"/>
     </row>
     <row r="14" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D14" s="467"/>
+      <c r="D14" s="462"/>
       <c r="E14" s="434" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="468" t="s">
+      <c r="F14" s="465" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="469"/>
-      <c r="H14" s="469"/>
-      <c r="I14" s="469"/>
-      <c r="J14" s="469"/>
-      <c r="K14" s="470"/>
+      <c r="G14" s="466"/>
+      <c r="H14" s="466"/>
+      <c r="I14" s="466"/>
+      <c r="J14" s="466"/>
+      <c r="K14" s="467"/>
       <c r="O14" s="439"/>
       <c r="P14" s="439"/>
     </row>
     <row r="15" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D15" s="467"/>
+      <c r="D15" s="462"/>
       <c r="E15" s="437" t="s">
         <v>17</v>
       </c>
@@ -5221,7 +5237,7 @@
       <c r="P15" s="439"/>
     </row>
     <row r="16" spans="4:17" ht="24.95" hidden="1" customHeight="1">
-      <c r="D16" s="467"/>
+      <c r="D16" s="462"/>
       <c r="E16" s="437" t="s">
         <v>28</v>
       </c>
@@ -5238,7 +5254,7 @@
       <c r="Q16" s="463"/>
     </row>
     <row r="17" spans="4:17" ht="24.95" hidden="1" customHeight="1">
-      <c r="D17" s="467"/>
+      <c r="D17" s="462"/>
       <c r="E17" s="437" t="s">
         <v>28</v>
       </c>
@@ -5255,7 +5271,7 @@
       <c r="Q17" s="439"/>
     </row>
     <row r="18" spans="4:17" ht="24.95" hidden="1" customHeight="1">
-      <c r="D18" s="467"/>
+      <c r="D18" s="462"/>
       <c r="E18" s="437" t="s">
         <v>28</v>
       </c>
@@ -5272,7 +5288,7 @@
       <c r="Q18" s="440"/>
     </row>
     <row r="19" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D19" s="467"/>
+      <c r="D19" s="462"/>
       <c r="E19" s="434" t="s">
         <v>19</v>
       </c>
@@ -5394,12 +5410,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D13:D19"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="F12:K12"/>
-    <mergeCell ref="F14:K14"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="F19:K19"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="F5:K5"/>
@@ -5407,6 +5417,12 @@
     <mergeCell ref="F10:K10"/>
     <mergeCell ref="D4:D8"/>
     <mergeCell ref="D9:D12"/>
+    <mergeCell ref="D13:D19"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="F12:K12"/>
+    <mergeCell ref="F14:K14"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="F19:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -5427,22 +5443,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21">
-      <c r="A1" s="471" t="s">
+      <c r="A1" s="483" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="471"/>
-      <c r="C1" s="471"/>
-      <c r="D1" s="471"/>
-      <c r="E1" s="471"/>
+      <c r="B1" s="483"/>
+      <c r="C1" s="483"/>
+      <c r="D1" s="483"/>
+      <c r="E1" s="483"/>
     </row>
     <row r="2" spans="1:6" ht="21">
-      <c r="A2" s="471" t="s">
+      <c r="A2" s="483" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="471"/>
-      <c r="C2" s="471"/>
-      <c r="D2" s="471"/>
-      <c r="E2" s="471"/>
+      <c r="B2" s="483"/>
+      <c r="C2" s="483"/>
+      <c r="D2" s="483"/>
+      <c r="E2" s="483"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="406"/>
@@ -5469,13 +5485,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
-      <c r="A5" s="472">
+      <c r="A5" s="484">
         <v>1</v>
       </c>
-      <c r="B5" s="475" t="s">
+      <c r="B5" s="486" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="475" t="s">
+      <c r="C5" s="486" t="s">
         <v>52</v>
       </c>
       <c r="D5" s="408" t="s">
@@ -5486,9 +5502,9 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
-      <c r="A6" s="472"/>
-      <c r="B6" s="475"/>
-      <c r="C6" s="475"/>
+      <c r="A6" s="484"/>
+      <c r="B6" s="486"/>
+      <c r="C6" s="486"/>
       <c r="D6" s="408" t="s">
         <v>55</v>
       </c>
@@ -5497,27 +5513,27 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="472"/>
-      <c r="B7" s="475"/>
-      <c r="C7" s="475"/>
-      <c r="D7" s="478" t="s">
+      <c r="A7" s="484"/>
+      <c r="B7" s="486"/>
+      <c r="C7" s="486"/>
+      <c r="D7" s="473" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="478" t="s">
+      <c r="E7" s="473" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="0.75" customHeight="1">
-      <c r="A8" s="472"/>
-      <c r="B8" s="475"/>
-      <c r="C8" s="475"/>
-      <c r="D8" s="478"/>
-      <c r="E8" s="478"/>
+      <c r="A8" s="484"/>
+      <c r="B8" s="486"/>
+      <c r="C8" s="486"/>
+      <c r="D8" s="473"/>
+      <c r="E8" s="473"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="472"/>
-      <c r="B9" s="475"/>
-      <c r="C9" s="475"/>
+      <c r="A9" s="484"/>
+      <c r="B9" s="486"/>
+      <c r="C9" s="486"/>
       <c r="D9" s="408" t="s">
         <v>59</v>
       </c>
@@ -5526,9 +5542,9 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
-      <c r="A10" s="472"/>
-      <c r="B10" s="475"/>
-      <c r="C10" s="475"/>
+      <c r="A10" s="484"/>
+      <c r="B10" s="486"/>
+      <c r="C10" s="486"/>
       <c r="D10" s="408" t="s">
         <v>61</v>
       </c>
@@ -5538,9 +5554,9 @@
       <c r="F10" s="409"/>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
-      <c r="A11" s="472"/>
-      <c r="B11" s="475"/>
-      <c r="C11" s="475"/>
+      <c r="A11" s="484"/>
+      <c r="B11" s="486"/>
+      <c r="C11" s="486"/>
       <c r="D11" s="408" t="s">
         <v>63</v>
       </c>
@@ -5549,36 +5565,36 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
-      <c r="A12" s="472"/>
-      <c r="B12" s="475"/>
-      <c r="C12" s="475"/>
+      <c r="A12" s="484"/>
+      <c r="B12" s="486"/>
+      <c r="C12" s="486"/>
       <c r="D12" s="408"/>
       <c r="E12" s="408" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
-      <c r="A13" s="472"/>
-      <c r="B13" s="475"/>
-      <c r="C13" s="475"/>
+      <c r="A13" s="484"/>
+      <c r="B13" s="486"/>
+      <c r="C13" s="486"/>
       <c r="D13" s="408"/>
       <c r="E13" s="408" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1">
-      <c r="A14" s="472"/>
-      <c r="B14" s="475"/>
-      <c r="C14" s="475"/>
+      <c r="A14" s="484"/>
+      <c r="B14" s="486"/>
+      <c r="C14" s="486"/>
       <c r="D14" s="408"/>
       <c r="E14" s="408" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1">
-      <c r="A15" s="472"/>
-      <c r="B15" s="475"/>
-      <c r="C15" s="475"/>
+      <c r="A15" s="484"/>
+      <c r="B15" s="486"/>
+      <c r="C15" s="486"/>
       <c r="D15" s="408" t="s">
         <v>68</v>
       </c>
@@ -5590,13 +5606,13 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1">
-      <c r="A16" s="473">
+      <c r="A16" s="485">
         <v>2</v>
       </c>
-      <c r="B16" s="476" t="s">
+      <c r="B16" s="487" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="476" t="s">
+      <c r="C16" s="487" t="s">
         <v>71</v>
       </c>
       <c r="D16" s="410" t="s">
@@ -5607,10 +5623,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
-      <c r="A17" s="473"/>
-      <c r="B17" s="476"/>
-      <c r="C17" s="476"/>
-      <c r="D17" s="479" t="s">
+      <c r="A17" s="485"/>
+      <c r="B17" s="487"/>
+      <c r="C17" s="487"/>
+      <c r="D17" s="489" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="410" t="s">
@@ -5618,91 +5634,91 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1">
-      <c r="A18" s="473"/>
-      <c r="B18" s="476"/>
-      <c r="C18" s="476"/>
-      <c r="D18" s="479"/>
+      <c r="A18" s="485"/>
+      <c r="B18" s="487"/>
+      <c r="C18" s="487"/>
+      <c r="D18" s="489"/>
       <c r="E18" s="410" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1">
-      <c r="A19" s="473"/>
-      <c r="B19" s="476"/>
-      <c r="C19" s="476"/>
-      <c r="D19" s="479"/>
+      <c r="A19" s="485"/>
+      <c r="B19" s="487"/>
+      <c r="C19" s="487"/>
+      <c r="D19" s="489"/>
       <c r="E19" s="410" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
-      <c r="A20" s="473"/>
-      <c r="B20" s="476"/>
-      <c r="C20" s="476"/>
-      <c r="D20" s="479"/>
+      <c r="A20" s="485"/>
+      <c r="B20" s="487"/>
+      <c r="C20" s="487"/>
+      <c r="D20" s="489"/>
       <c r="E20" s="410" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1">
-      <c r="A21" s="473"/>
-      <c r="B21" s="476"/>
-      <c r="C21" s="476"/>
-      <c r="D21" s="479"/>
+      <c r="A21" s="485"/>
+      <c r="B21" s="487"/>
+      <c r="C21" s="487"/>
+      <c r="D21" s="489"/>
       <c r="E21" s="410" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
-      <c r="A22" s="473"/>
-      <c r="B22" s="476"/>
-      <c r="C22" s="476"/>
-      <c r="D22" s="479"/>
+      <c r="A22" s="485"/>
+      <c r="B22" s="487"/>
+      <c r="C22" s="487"/>
+      <c r="D22" s="489"/>
       <c r="E22" s="410" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1">
-      <c r="A23" s="473"/>
-      <c r="B23" s="476"/>
-      <c r="C23" s="476"/>
-      <c r="D23" s="479"/>
+      <c r="A23" s="485"/>
+      <c r="B23" s="487"/>
+      <c r="C23" s="487"/>
+      <c r="D23" s="489"/>
       <c r="E23" s="410" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1">
-      <c r="A24" s="473"/>
-      <c r="B24" s="476"/>
-      <c r="C24" s="476"/>
-      <c r="D24" s="479"/>
+      <c r="A24" s="485"/>
+      <c r="B24" s="487"/>
+      <c r="C24" s="487"/>
+      <c r="D24" s="489"/>
       <c r="E24" s="410" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1">
-      <c r="A25" s="473"/>
-      <c r="B25" s="476"/>
-      <c r="C25" s="476"/>
-      <c r="D25" s="479"/>
+      <c r="A25" s="485"/>
+      <c r="B25" s="487"/>
+      <c r="C25" s="487"/>
+      <c r="D25" s="489"/>
       <c r="E25" s="410" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1">
-      <c r="A26" s="473"/>
-      <c r="B26" s="476"/>
-      <c r="C26" s="476"/>
-      <c r="D26" s="479"/>
+      <c r="A26" s="485"/>
+      <c r="B26" s="487"/>
+      <c r="C26" s="487"/>
+      <c r="D26" s="489"/>
       <c r="E26" s="410" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" hidden="1" customHeight="1">
-      <c r="A27" s="474">
+      <c r="A27" s="480">
         <v>3</v>
       </c>
-      <c r="B27" s="477" t="s">
+      <c r="B27" s="488" t="s">
         <v>82</v>
       </c>
       <c r="C27" s="412"/>
@@ -5714,8 +5730,8 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" hidden="1" customHeight="1">
-      <c r="A28" s="474"/>
-      <c r="B28" s="477"/>
+      <c r="A28" s="480"/>
+      <c r="B28" s="488"/>
       <c r="C28" s="412"/>
       <c r="D28" s="413" t="s">
         <v>84</v>
@@ -5725,8 +5741,8 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" hidden="1" customHeight="1">
-      <c r="A29" s="474"/>
-      <c r="B29" s="477"/>
+      <c r="A29" s="480"/>
+      <c r="B29" s="488"/>
       <c r="C29" s="412"/>
       <c r="D29" s="413" t="s">
         <v>73</v>
@@ -5736,8 +5752,8 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" hidden="1" customHeight="1">
-      <c r="A30" s="474"/>
-      <c r="B30" s="477"/>
+      <c r="A30" s="480"/>
+      <c r="B30" s="488"/>
       <c r="C30" s="412"/>
       <c r="D30" s="413"/>
       <c r="E30" s="413" t="s">
@@ -5745,8 +5761,8 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="0.75" hidden="1" customHeight="1">
-      <c r="A31" s="474"/>
-      <c r="B31" s="477"/>
+      <c r="A31" s="480"/>
+      <c r="B31" s="488"/>
       <c r="C31" s="412"/>
       <c r="D31" s="413"/>
       <c r="E31" s="413" t="s">
@@ -5754,8 +5770,8 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="61.5" hidden="1" customHeight="1">
-      <c r="A32" s="474"/>
-      <c r="B32" s="477"/>
+      <c r="A32" s="480"/>
+      <c r="B32" s="488"/>
       <c r="C32" s="412"/>
       <c r="D32" s="413"/>
       <c r="E32" s="413" t="s">
@@ -5763,13 +5779,13 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
-      <c r="A33" s="480">
+      <c r="A33" s="481">
         <v>4</v>
       </c>
-      <c r="B33" s="483" t="s">
+      <c r="B33" s="477" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="483" t="s">
+      <c r="C33" s="477" t="s">
         <v>91</v>
       </c>
       <c r="D33" s="415" t="s">
@@ -5780,9 +5796,9 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="480"/>
-      <c r="B34" s="483"/>
-      <c r="C34" s="483"/>
+      <c r="A34" s="481"/>
+      <c r="B34" s="477"/>
+      <c r="C34" s="477"/>
       <c r="D34" s="415" t="s">
         <v>92</v>
       </c>
@@ -5791,9 +5807,9 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="480"/>
-      <c r="B35" s="483"/>
-      <c r="C35" s="483"/>
+      <c r="A35" s="481"/>
+      <c r="B35" s="477"/>
+      <c r="C35" s="477"/>
       <c r="D35" s="415" t="s">
         <v>59</v>
       </c>
@@ -5802,9 +5818,9 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="480"/>
-      <c r="B36" s="483"/>
-      <c r="C36" s="483"/>
+      <c r="A36" s="481"/>
+      <c r="B36" s="477"/>
+      <c r="C36" s="477"/>
       <c r="D36" s="415" t="s">
         <v>94</v>
       </c>
@@ -5813,10 +5829,10 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="480"/>
-      <c r="B37" s="483"/>
-      <c r="C37" s="483"/>
-      <c r="D37" s="487" t="s">
+      <c r="A37" s="481"/>
+      <c r="B37" s="477"/>
+      <c r="C37" s="477"/>
+      <c r="D37" s="474" t="s">
         <v>73</v>
       </c>
       <c r="E37" s="415" t="s">
@@ -5824,79 +5840,79 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="480"/>
-      <c r="B38" s="483"/>
-      <c r="C38" s="483"/>
-      <c r="D38" s="487"/>
+      <c r="A38" s="481"/>
+      <c r="B38" s="477"/>
+      <c r="C38" s="477"/>
+      <c r="D38" s="474"/>
       <c r="E38" s="415" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="480"/>
-      <c r="B39" s="483"/>
-      <c r="C39" s="483"/>
-      <c r="D39" s="487"/>
+      <c r="A39" s="481"/>
+      <c r="B39" s="477"/>
+      <c r="C39" s="477"/>
+      <c r="D39" s="474"/>
       <c r="E39" s="415" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A40" s="480"/>
-      <c r="B40" s="483"/>
-      <c r="C40" s="483"/>
-      <c r="D40" s="487"/>
+      <c r="A40" s="481"/>
+      <c r="B40" s="477"/>
+      <c r="C40" s="477"/>
+      <c r="D40" s="474"/>
       <c r="E40" s="415" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A41" s="480"/>
-      <c r="B41" s="483"/>
-      <c r="C41" s="483"/>
-      <c r="D41" s="487"/>
+      <c r="A41" s="481"/>
+      <c r="B41" s="477"/>
+      <c r="C41" s="477"/>
+      <c r="D41" s="474"/>
       <c r="E41" s="415" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="0.75" customHeight="1">
-      <c r="A42" s="480"/>
-      <c r="B42" s="483"/>
+      <c r="A42" s="481"/>
+      <c r="B42" s="477"/>
       <c r="C42" s="414"/>
-      <c r="D42" s="487"/>
+      <c r="D42" s="474"/>
       <c r="E42" s="415"/>
     </row>
     <row r="43" spans="1:5" hidden="1">
-      <c r="A43" s="480"/>
-      <c r="B43" s="483"/>
+      <c r="A43" s="481"/>
+      <c r="B43" s="477"/>
       <c r="C43" s="414"/>
-      <c r="D43" s="487"/>
-      <c r="E43" s="487"/>
+      <c r="D43" s="474"/>
+      <c r="E43" s="474"/>
     </row>
     <row r="44" spans="1:5" ht="3" hidden="1" customHeight="1">
-      <c r="A44" s="480"/>
-      <c r="B44" s="483"/>
+      <c r="A44" s="481"/>
+      <c r="B44" s="477"/>
       <c r="C44" s="414"/>
-      <c r="D44" s="487"/>
-      <c r="E44" s="487"/>
+      <c r="D44" s="474"/>
+      <c r="E44" s="474"/>
     </row>
     <row r="45" spans="1:5" hidden="1">
-      <c r="A45" s="480"/>
-      <c r="B45" s="483"/>
+      <c r="A45" s="481"/>
+      <c r="B45" s="477"/>
       <c r="C45" s="414"/>
-      <c r="D45" s="487"/>
+      <c r="D45" s="474"/>
       <c r="E45" s="415"/>
     </row>
     <row r="46" spans="1:5" hidden="1">
-      <c r="A46" s="480"/>
-      <c r="B46" s="483"/>
+      <c r="A46" s="481"/>
+      <c r="B46" s="477"/>
       <c r="C46" s="414"/>
-      <c r="D46" s="487"/>
+      <c r="D46" s="474"/>
       <c r="E46" s="415"/>
     </row>
     <row r="47" spans="1:5" hidden="1">
-      <c r="A47" s="480"/>
-      <c r="B47" s="483"/>
+      <c r="A47" s="481"/>
+      <c r="B47" s="477"/>
       <c r="C47" s="414"/>
       <c r="D47" s="416" t="s">
         <v>97</v>
@@ -5906,8 +5922,8 @@
       </c>
     </row>
     <row r="48" spans="1:5" ht="2.25" customHeight="1">
-      <c r="A48" s="480"/>
-      <c r="B48" s="483"/>
+      <c r="A48" s="481"/>
+      <c r="B48" s="477"/>
       <c r="C48" s="414"/>
       <c r="D48" s="416" t="s">
         <v>99</v>
@@ -5927,7 +5943,7 @@
       <c r="D49" s="419" t="s">
         <v>53</v>
       </c>
-      <c r="E49" s="488" t="s">
+      <c r="E49" s="475" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5942,16 +5958,16 @@
       <c r="D50" s="419" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="488"/>
+      <c r="E50" s="475"/>
     </row>
     <row r="51" spans="1:6" s="405" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A51" s="481">
+      <c r="A51" s="478">
         <v>5</v>
       </c>
-      <c r="B51" s="481" t="s">
+      <c r="B51" s="478" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="481" t="s">
+      <c r="C51" s="478" t="s">
         <v>105</v>
       </c>
       <c r="D51" s="420" t="s">
@@ -5962,9 +5978,9 @@
       </c>
     </row>
     <row r="52" spans="1:6" s="405" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A52" s="481"/>
-      <c r="B52" s="481"/>
-      <c r="C52" s="481"/>
+      <c r="A52" s="478"/>
+      <c r="B52" s="478"/>
+      <c r="C52" s="478"/>
       <c r="D52" s="420" t="s">
         <v>92</v>
       </c>
@@ -5973,9 +5989,9 @@
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="481"/>
-      <c r="B53" s="481"/>
-      <c r="C53" s="481"/>
+      <c r="A53" s="478"/>
+      <c r="B53" s="478"/>
+      <c r="C53" s="478"/>
       <c r="D53" s="421" t="s">
         <v>59</v>
       </c>
@@ -5984,10 +6000,10 @@
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="481"/>
-      <c r="B54" s="481"/>
-      <c r="C54" s="481"/>
-      <c r="D54" s="489" t="s">
+      <c r="A54" s="478"/>
+      <c r="B54" s="478"/>
+      <c r="C54" s="478"/>
+      <c r="D54" s="476" t="s">
         <v>73</v>
       </c>
       <c r="E54" s="420" t="s">
@@ -5995,37 +6011,37 @@
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="481"/>
-      <c r="B55" s="481"/>
-      <c r="C55" s="481"/>
-      <c r="D55" s="489"/>
+      <c r="A55" s="478"/>
+      <c r="B55" s="478"/>
+      <c r="C55" s="478"/>
+      <c r="D55" s="476"/>
       <c r="E55" s="420" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="481"/>
-      <c r="B56" s="481"/>
-      <c r="C56" s="481"/>
-      <c r="D56" s="489"/>
+      <c r="A56" s="478"/>
+      <c r="B56" s="478"/>
+      <c r="C56" s="478"/>
+      <c r="D56" s="476"/>
       <c r="E56" s="420" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="481"/>
-      <c r="B57" s="481"/>
-      <c r="C57" s="481"/>
-      <c r="D57" s="489"/>
+      <c r="A57" s="478"/>
+      <c r="B57" s="478"/>
+      <c r="C57" s="478"/>
+      <c r="D57" s="476"/>
       <c r="E57" s="420" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="481"/>
-      <c r="B58" s="481"/>
-      <c r="C58" s="481"/>
-      <c r="D58" s="489"/>
+      <c r="A58" s="478"/>
+      <c r="B58" s="478"/>
+      <c r="C58" s="478"/>
+      <c r="D58" s="476"/>
       <c r="E58" s="420" t="s">
         <v>96</v>
       </c>
@@ -6034,10 +6050,10 @@
       <c r="A59" s="482">
         <v>6</v>
       </c>
-      <c r="B59" s="484" t="s">
+      <c r="B59" s="479" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="484" t="s">
+      <c r="C59" s="479" t="s">
         <v>71</v>
       </c>
       <c r="D59" s="423" t="s">
@@ -6052,9 +6068,9 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="482"/>
-      <c r="B60" s="484"/>
-      <c r="C60" s="484"/>
-      <c r="D60" s="486" t="s">
+      <c r="B60" s="479"/>
+      <c r="C60" s="479"/>
+      <c r="D60" s="472" t="s">
         <v>92</v>
       </c>
       <c r="E60" s="424" t="s">
@@ -6066,15 +6082,15 @@
     </row>
     <row r="61" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A61" s="482"/>
-      <c r="B61" s="484"/>
-      <c r="C61" s="484"/>
-      <c r="D61" s="486"/>
+      <c r="B61" s="479"/>
+      <c r="C61" s="479"/>
+      <c r="D61" s="472"/>
       <c r="E61" s="424"/>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="482"/>
-      <c r="B62" s="484"/>
-      <c r="C62" s="484"/>
+      <c r="B62" s="479"/>
+      <c r="C62" s="479"/>
       <c r="D62" s="423" t="s">
         <v>59</v>
       </c>
@@ -6087,9 +6103,9 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="482"/>
-      <c r="B63" s="484"/>
-      <c r="C63" s="484"/>
-      <c r="D63" s="486" t="s">
+      <c r="B63" s="479"/>
+      <c r="C63" s="479"/>
+      <c r="D63" s="472" t="s">
         <v>73</v>
       </c>
       <c r="E63" s="424" t="s">
@@ -6101,94 +6117,94 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="482"/>
-      <c r="B64" s="484"/>
-      <c r="C64" s="484"/>
-      <c r="D64" s="486"/>
+      <c r="B64" s="479"/>
+      <c r="C64" s="479"/>
+      <c r="D64" s="472"/>
       <c r="E64" s="424" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="482"/>
-      <c r="B65" s="484"/>
-      <c r="C65" s="484"/>
-      <c r="D65" s="486"/>
+      <c r="B65" s="479"/>
+      <c r="C65" s="479"/>
+      <c r="D65" s="472"/>
       <c r="E65" s="424"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="482"/>
-      <c r="B66" s="484"/>
-      <c r="C66" s="484"/>
-      <c r="D66" s="486"/>
+      <c r="B66" s="479"/>
+      <c r="C66" s="479"/>
+      <c r="D66" s="472"/>
       <c r="E66" s="424" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="482"/>
-      <c r="B67" s="484"/>
-      <c r="C67" s="484"/>
-      <c r="D67" s="486"/>
+      <c r="B67" s="479"/>
+      <c r="C67" s="479"/>
+      <c r="D67" s="472"/>
       <c r="E67" s="424" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="482"/>
-      <c r="B68" s="484"/>
-      <c r="C68" s="484"/>
-      <c r="D68" s="486"/>
+      <c r="B68" s="479"/>
+      <c r="C68" s="479"/>
+      <c r="D68" s="472"/>
       <c r="E68" s="424" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="482"/>
-      <c r="B69" s="484"/>
-      <c r="C69" s="484"/>
-      <c r="D69" s="486"/>
+      <c r="B69" s="479"/>
+      <c r="C69" s="479"/>
+      <c r="D69" s="472"/>
       <c r="E69" s="424" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="482"/>
-      <c r="B70" s="484"/>
-      <c r="C70" s="484"/>
-      <c r="D70" s="486"/>
+      <c r="B70" s="479"/>
+      <c r="C70" s="479"/>
+      <c r="D70" s="472"/>
       <c r="E70" s="424" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:5" hidden="1">
       <c r="A71" s="482"/>
-      <c r="B71" s="484"/>
+      <c r="B71" s="479"/>
       <c r="C71" s="422"/>
-      <c r="D71" s="486"/>
+      <c r="D71" s="472"/>
       <c r="E71" s="424"/>
     </row>
     <row r="72" spans="1:5" hidden="1">
       <c r="A72" s="482"/>
-      <c r="B72" s="484"/>
+      <c r="B72" s="479"/>
       <c r="C72" s="422"/>
-      <c r="D72" s="486"/>
+      <c r="D72" s="472"/>
       <c r="E72" s="424"/>
     </row>
     <row r="73" spans="1:5" hidden="1">
       <c r="A73" s="482"/>
-      <c r="B73" s="484"/>
+      <c r="B73" s="479"/>
       <c r="C73" s="422"/>
-      <c r="D73" s="486"/>
+      <c r="D73" s="472"/>
       <c r="E73" s="424"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="474">
+      <c r="A74" s="480">
         <v>7</v>
       </c>
-      <c r="B74" s="474" t="s">
+      <c r="B74" s="480" t="s">
         <v>115</v>
       </c>
-      <c r="C74" s="474" t="s">
+      <c r="C74" s="480" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="426" t="s">
@@ -6199,10 +6215,10 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="474"/>
-      <c r="B75" s="474"/>
-      <c r="C75" s="474"/>
-      <c r="D75" s="485" t="s">
+      <c r="A75" s="480"/>
+      <c r="B75" s="480"/>
+      <c r="C75" s="480"/>
+      <c r="D75" s="471" t="s">
         <v>92</v>
       </c>
       <c r="E75" s="413" t="s">
@@ -6210,16 +6226,16 @@
       </c>
     </row>
     <row r="76" spans="1:5" ht="0.75" customHeight="1">
-      <c r="A76" s="474"/>
-      <c r="B76" s="474"/>
-      <c r="C76" s="474"/>
-      <c r="D76" s="485"/>
+      <c r="A76" s="480"/>
+      <c r="B76" s="480"/>
+      <c r="C76" s="480"/>
+      <c r="D76" s="471"/>
       <c r="E76" s="413"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="474"/>
-      <c r="B77" s="474"/>
-      <c r="C77" s="474"/>
+      <c r="A77" s="480"/>
+      <c r="B77" s="480"/>
+      <c r="C77" s="480"/>
       <c r="D77" s="426" t="s">
         <v>59</v>
       </c>
@@ -6228,9 +6244,9 @@
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="474"/>
-      <c r="B78" s="474"/>
-      <c r="C78" s="474"/>
+      <c r="A78" s="480"/>
+      <c r="B78" s="480"/>
+      <c r="C78" s="480"/>
       <c r="D78" s="426" t="s">
         <v>117</v>
       </c>
@@ -6239,10 +6255,10 @@
       </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="474"/>
-      <c r="B79" s="474"/>
-      <c r="C79" s="474"/>
-      <c r="D79" s="485" t="s">
+      <c r="A79" s="480"/>
+      <c r="B79" s="480"/>
+      <c r="C79" s="480"/>
+      <c r="D79" s="471" t="s">
         <v>73</v>
       </c>
       <c r="E79" s="413" t="s">
@@ -6250,90 +6266,90 @@
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="474"/>
-      <c r="B80" s="474"/>
-      <c r="C80" s="474"/>
-      <c r="D80" s="485"/>
+      <c r="A80" s="480"/>
+      <c r="B80" s="480"/>
+      <c r="C80" s="480"/>
+      <c r="D80" s="471"/>
       <c r="E80" s="413" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="474"/>
-      <c r="B81" s="474"/>
-      <c r="C81" s="474"/>
-      <c r="D81" s="485"/>
+      <c r="A81" s="480"/>
+      <c r="B81" s="480"/>
+      <c r="C81" s="480"/>
+      <c r="D81" s="471"/>
       <c r="E81" s="413" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="474"/>
-      <c r="B82" s="474"/>
-      <c r="C82" s="474"/>
-      <c r="D82" s="485"/>
+      <c r="A82" s="480"/>
+      <c r="B82" s="480"/>
+      <c r="C82" s="480"/>
+      <c r="D82" s="471"/>
       <c r="E82" s="413" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="474"/>
-      <c r="B83" s="474"/>
-      <c r="C83" s="474"/>
-      <c r="D83" s="485"/>
+      <c r="A83" s="480"/>
+      <c r="B83" s="480"/>
+      <c r="C83" s="480"/>
+      <c r="D83" s="471"/>
       <c r="E83" s="413" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="474"/>
-      <c r="B84" s="474"/>
-      <c r="C84" s="474"/>
-      <c r="D84" s="485"/>
+      <c r="A84" s="480"/>
+      <c r="B84" s="480"/>
+      <c r="C84" s="480"/>
+      <c r="D84" s="471"/>
       <c r="E84" s="413" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="474"/>
-      <c r="B85" s="474"/>
-      <c r="C85" s="474"/>
-      <c r="D85" s="485"/>
+      <c r="A85" s="480"/>
+      <c r="B85" s="480"/>
+      <c r="C85" s="480"/>
+      <c r="D85" s="471"/>
       <c r="E85" s="413" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="474"/>
-      <c r="B86" s="474"/>
-      <c r="C86" s="474"/>
-      <c r="D86" s="485"/>
+      <c r="A86" s="480"/>
+      <c r="B86" s="480"/>
+      <c r="C86" s="480"/>
+      <c r="D86" s="471"/>
       <c r="E86" s="413" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:5" hidden="1">
-      <c r="A87" s="474"/>
-      <c r="B87" s="474"/>
+      <c r="A87" s="480"/>
+      <c r="B87" s="480"/>
       <c r="C87" s="411"/>
-      <c r="D87" s="485"/>
+      <c r="D87" s="471"/>
       <c r="E87" s="413"/>
     </row>
     <row r="88" spans="1:5" hidden="1">
-      <c r="A88" s="474"/>
-      <c r="B88" s="474"/>
+      <c r="A88" s="480"/>
+      <c r="B88" s="480"/>
       <c r="C88" s="411"/>
-      <c r="D88" s="485"/>
+      <c r="D88" s="471"/>
       <c r="E88" s="413"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="482">
         <v>8</v>
       </c>
-      <c r="B89" s="484" t="s">
+      <c r="B89" s="479" t="s">
         <v>118</v>
       </c>
-      <c r="C89" s="484" t="s">
+      <c r="C89" s="479" t="s">
         <v>71</v>
       </c>
       <c r="D89" s="423" t="s">
@@ -6345,8 +6361,8 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="482"/>
-      <c r="B90" s="484"/>
-      <c r="C90" s="484"/>
+      <c r="B90" s="479"/>
+      <c r="C90" s="479"/>
       <c r="D90" s="425" t="s">
         <v>92</v>
       </c>
@@ -6356,8 +6372,8 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="482"/>
-      <c r="B91" s="484"/>
-      <c r="C91" s="484"/>
+      <c r="B91" s="479"/>
+      <c r="C91" s="479"/>
       <c r="D91" s="423" t="s">
         <v>59</v>
       </c>
@@ -6367,9 +6383,9 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="482"/>
-      <c r="B92" s="484"/>
-      <c r="C92" s="484"/>
-      <c r="D92" s="486" t="s">
+      <c r="B92" s="479"/>
+      <c r="C92" s="479"/>
+      <c r="D92" s="472" t="s">
         <v>73</v>
       </c>
       <c r="E92" s="424" t="s">
@@ -6378,75 +6394,49 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="482"/>
-      <c r="B93" s="484"/>
-      <c r="C93" s="484"/>
-      <c r="D93" s="486"/>
+      <c r="B93" s="479"/>
+      <c r="C93" s="479"/>
+      <c r="D93" s="472"/>
       <c r="E93" s="424" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="482"/>
-      <c r="B94" s="484"/>
-      <c r="C94" s="484"/>
-      <c r="D94" s="486"/>
+      <c r="B94" s="479"/>
+      <c r="C94" s="479"/>
+      <c r="D94" s="472"/>
       <c r="E94" s="424"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="482"/>
-      <c r="B95" s="484"/>
-      <c r="C95" s="484"/>
-      <c r="D95" s="486"/>
+      <c r="B95" s="479"/>
+      <c r="C95" s="479"/>
+      <c r="D95" s="472"/>
       <c r="E95" s="424" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="482"/>
-      <c r="B96" s="484"/>
-      <c r="C96" s="484"/>
-      <c r="D96" s="486"/>
+      <c r="B96" s="479"/>
+      <c r="C96" s="479"/>
+      <c r="D96" s="472"/>
       <c r="E96" s="424" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="482"/>
-      <c r="B97" s="484"/>
-      <c r="C97" s="484"/>
-      <c r="D97" s="486"/>
+      <c r="B97" s="479"/>
+      <c r="C97" s="479"/>
+      <c r="D97" s="472"/>
       <c r="E97" s="424" t="s">
         <v>113</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="D79:D88"/>
-    <mergeCell ref="D92:D97"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="D37:D42"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="D63:D73"/>
-    <mergeCell ref="C33:C41"/>
-    <mergeCell ref="C51:C58"/>
-    <mergeCell ref="C59:C70"/>
-    <mergeCell ref="C74:C86"/>
-    <mergeCell ref="C89:C97"/>
-    <mergeCell ref="B33:B48"/>
-    <mergeCell ref="B51:B58"/>
-    <mergeCell ref="B59:B73"/>
-    <mergeCell ref="B74:B88"/>
-    <mergeCell ref="B89:B97"/>
-    <mergeCell ref="A33:A48"/>
-    <mergeCell ref="A51:A58"/>
-    <mergeCell ref="A59:A73"/>
-    <mergeCell ref="A74:A88"/>
-    <mergeCell ref="A89:A97"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A5:A15"/>
@@ -6459,6 +6449,32 @@
     <mergeCell ref="C16:C26"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D17:D26"/>
+    <mergeCell ref="A33:A48"/>
+    <mergeCell ref="A51:A58"/>
+    <mergeCell ref="A59:A73"/>
+    <mergeCell ref="A74:A88"/>
+    <mergeCell ref="A89:A97"/>
+    <mergeCell ref="B33:B48"/>
+    <mergeCell ref="B51:B58"/>
+    <mergeCell ref="B59:B73"/>
+    <mergeCell ref="B74:B88"/>
+    <mergeCell ref="B89:B97"/>
+    <mergeCell ref="C33:C41"/>
+    <mergeCell ref="C51:C58"/>
+    <mergeCell ref="C59:C70"/>
+    <mergeCell ref="C74:C86"/>
+    <mergeCell ref="C89:C97"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="D79:D88"/>
+    <mergeCell ref="D92:D97"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="D37:D42"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D54:D58"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="D63:D73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7173,81 +7189,81 @@
     </row>
     <row r="3" spans="3:33" ht="5.25" customHeight="1"/>
     <row r="4" spans="3:33" ht="14.1" customHeight="1">
-      <c r="C4" s="491" t="s">
+      <c r="C4" s="503" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="491"/>
-      <c r="E4" s="491"/>
-      <c r="F4" s="491"/>
-      <c r="G4" s="491"/>
-      <c r="H4" s="491"/>
-      <c r="I4" s="491"/>
-      <c r="J4" s="491"/>
-      <c r="K4" s="491"/>
-      <c r="L4" s="491"/>
-      <c r="M4" s="491"/>
-      <c r="N4" s="491"/>
-      <c r="O4" s="491"/>
-      <c r="P4" s="491"/>
-      <c r="Q4" s="491"/>
-      <c r="R4" s="491"/>
-      <c r="S4" s="491"/>
-      <c r="T4" s="491"/>
-      <c r="U4" s="491"/>
-      <c r="V4" s="491"/>
-      <c r="W4" s="491"/>
-      <c r="X4" s="491"/>
-      <c r="Y4" s="491"/>
-      <c r="Z4" s="491"/>
-      <c r="AA4" s="491"/>
-      <c r="AB4" s="491"/>
-      <c r="AC4" s="491"/>
-      <c r="AD4" s="491"/>
-      <c r="AE4" s="491"/>
-      <c r="AF4" s="491"/>
-      <c r="AG4" s="491"/>
+      <c r="D4" s="503"/>
+      <c r="E4" s="503"/>
+      <c r="F4" s="503"/>
+      <c r="G4" s="503"/>
+      <c r="H4" s="503"/>
+      <c r="I4" s="503"/>
+      <c r="J4" s="503"/>
+      <c r="K4" s="503"/>
+      <c r="L4" s="503"/>
+      <c r="M4" s="503"/>
+      <c r="N4" s="503"/>
+      <c r="O4" s="503"/>
+      <c r="P4" s="503"/>
+      <c r="Q4" s="503"/>
+      <c r="R4" s="503"/>
+      <c r="S4" s="503"/>
+      <c r="T4" s="503"/>
+      <c r="U4" s="503"/>
+      <c r="V4" s="503"/>
+      <c r="W4" s="503"/>
+      <c r="X4" s="503"/>
+      <c r="Y4" s="503"/>
+      <c r="Z4" s="503"/>
+      <c r="AA4" s="503"/>
+      <c r="AB4" s="503"/>
+      <c r="AC4" s="503"/>
+      <c r="AD4" s="503"/>
+      <c r="AE4" s="503"/>
+      <c r="AF4" s="503"/>
+      <c r="AG4" s="503"/>
     </row>
     <row r="5" spans="3:33" ht="6.95" customHeight="1"/>
     <row r="6" spans="3:33" ht="15" customHeight="1">
-      <c r="C6" s="492">
+      <c r="C6" s="499">
         <v>46204</v>
       </c>
-      <c r="D6" s="493"/>
-      <c r="E6" s="493"/>
-      <c r="F6" s="493"/>
-      <c r="G6" s="493"/>
-      <c r="H6" s="493"/>
-      <c r="I6" s="494"/>
+      <c r="D6" s="500"/>
+      <c r="E6" s="500"/>
+      <c r="F6" s="500"/>
+      <c r="G6" s="500"/>
+      <c r="H6" s="500"/>
+      <c r="I6" s="501"/>
       <c r="J6" s="279"/>
-      <c r="K6" s="492">
+      <c r="K6" s="499">
         <v>46235</v>
       </c>
-      <c r="L6" s="493"/>
-      <c r="M6" s="493"/>
-      <c r="N6" s="493"/>
-      <c r="O6" s="493"/>
-      <c r="P6" s="493"/>
-      <c r="Q6" s="494"/>
+      <c r="L6" s="500"/>
+      <c r="M6" s="500"/>
+      <c r="N6" s="500"/>
+      <c r="O6" s="500"/>
+      <c r="P6" s="500"/>
+      <c r="Q6" s="501"/>
       <c r="R6" s="279"/>
-      <c r="S6" s="492">
+      <c r="S6" s="499">
         <v>46266</v>
       </c>
-      <c r="T6" s="493"/>
-      <c r="U6" s="493"/>
-      <c r="V6" s="493"/>
-      <c r="W6" s="493"/>
-      <c r="X6" s="493"/>
-      <c r="Y6" s="494"/>
+      <c r="T6" s="500"/>
+      <c r="U6" s="500"/>
+      <c r="V6" s="500"/>
+      <c r="W6" s="500"/>
+      <c r="X6" s="500"/>
+      <c r="Y6" s="501"/>
       <c r="Z6" s="279"/>
-      <c r="AA6" s="492">
+      <c r="AA6" s="499">
         <v>46296</v>
       </c>
-      <c r="AB6" s="493"/>
-      <c r="AC6" s="493"/>
-      <c r="AD6" s="493"/>
-      <c r="AE6" s="493"/>
-      <c r="AF6" s="493"/>
-      <c r="AG6" s="494"/>
+      <c r="AB6" s="500"/>
+      <c r="AC6" s="500"/>
+      <c r="AD6" s="500"/>
+      <c r="AE6" s="500"/>
+      <c r="AF6" s="500"/>
+      <c r="AG6" s="501"/>
     </row>
     <row r="7" spans="3:33" ht="15" customHeight="1">
       <c r="C7" s="280" t="s">
@@ -7877,34 +7893,34 @@
       </c>
     </row>
     <row r="14" spans="3:33" ht="9.9499999999999993" customHeight="1">
-      <c r="C14" s="499"/>
-      <c r="D14" s="495"/>
-      <c r="E14" s="495"/>
-      <c r="F14" s="495"/>
-      <c r="G14" s="495"/>
-      <c r="H14" s="495"/>
-      <c r="I14" s="496"/>
-      <c r="K14" s="500"/>
-      <c r="L14" s="501"/>
-      <c r="M14" s="497"/>
-      <c r="N14" s="502"/>
-      <c r="O14" s="501"/>
-      <c r="P14" s="497"/>
-      <c r="Q14" s="498"/>
-      <c r="S14" s="499"/>
-      <c r="T14" s="495"/>
-      <c r="U14" s="495"/>
-      <c r="V14" s="495"/>
-      <c r="W14" s="495"/>
-      <c r="X14" s="495"/>
-      <c r="Y14" s="496"/>
-      <c r="AA14" s="499"/>
-      <c r="AB14" s="495"/>
-      <c r="AC14" s="495"/>
-      <c r="AD14" s="495"/>
-      <c r="AE14" s="495"/>
-      <c r="AF14" s="495"/>
-      <c r="AG14" s="496"/>
+      <c r="C14" s="502"/>
+      <c r="D14" s="497"/>
+      <c r="E14" s="497"/>
+      <c r="F14" s="497"/>
+      <c r="G14" s="497"/>
+      <c r="H14" s="497"/>
+      <c r="I14" s="498"/>
+      <c r="K14" s="496"/>
+      <c r="L14" s="493"/>
+      <c r="M14" s="491"/>
+      <c r="N14" s="492"/>
+      <c r="O14" s="493"/>
+      <c r="P14" s="491"/>
+      <c r="Q14" s="494"/>
+      <c r="S14" s="502"/>
+      <c r="T14" s="497"/>
+      <c r="U14" s="497"/>
+      <c r="V14" s="497"/>
+      <c r="W14" s="497"/>
+      <c r="X14" s="497"/>
+      <c r="Y14" s="498"/>
+      <c r="AA14" s="502"/>
+      <c r="AB14" s="497"/>
+      <c r="AC14" s="497"/>
+      <c r="AD14" s="497"/>
+      <c r="AE14" s="497"/>
+      <c r="AF14" s="497"/>
+      <c r="AG14" s="498"/>
     </row>
     <row r="15" spans="3:33">
       <c r="C15" s="325"/>
@@ -8346,45 +8362,45 @@
     </row>
     <row r="26" spans="3:33" ht="6.95" customHeight="1"/>
     <row r="27" spans="3:33" ht="15" customHeight="1">
-      <c r="C27" s="492">
+      <c r="C27" s="499">
         <v>46327</v>
       </c>
-      <c r="D27" s="493"/>
-      <c r="E27" s="493"/>
-      <c r="F27" s="493"/>
-      <c r="G27" s="493"/>
-      <c r="H27" s="493"/>
-      <c r="I27" s="494"/>
+      <c r="D27" s="500"/>
+      <c r="E27" s="500"/>
+      <c r="F27" s="500"/>
+      <c r="G27" s="500"/>
+      <c r="H27" s="500"/>
+      <c r="I27" s="501"/>
       <c r="J27" s="279"/>
-      <c r="K27" s="492">
+      <c r="K27" s="499">
         <v>46357</v>
       </c>
-      <c r="L27" s="493"/>
-      <c r="M27" s="493"/>
-      <c r="N27" s="493"/>
-      <c r="O27" s="493"/>
-      <c r="P27" s="493"/>
-      <c r="Q27" s="494"/>
+      <c r="L27" s="500"/>
+      <c r="M27" s="500"/>
+      <c r="N27" s="500"/>
+      <c r="O27" s="500"/>
+      <c r="P27" s="500"/>
+      <c r="Q27" s="501"/>
       <c r="R27" s="279"/>
-      <c r="S27" s="492">
+      <c r="S27" s="499">
         <v>46388</v>
       </c>
-      <c r="T27" s="493"/>
-      <c r="U27" s="493"/>
-      <c r="V27" s="493"/>
-      <c r="W27" s="493"/>
-      <c r="X27" s="493"/>
-      <c r="Y27" s="494"/>
+      <c r="T27" s="500"/>
+      <c r="U27" s="500"/>
+      <c r="V27" s="500"/>
+      <c r="W27" s="500"/>
+      <c r="X27" s="500"/>
+      <c r="Y27" s="501"/>
       <c r="Z27" s="279"/>
-      <c r="AA27" s="492">
+      <c r="AA27" s="499">
         <v>46419</v>
       </c>
-      <c r="AB27" s="493"/>
-      <c r="AC27" s="493"/>
-      <c r="AD27" s="493"/>
-      <c r="AE27" s="493"/>
-      <c r="AF27" s="493"/>
-      <c r="AG27" s="494"/>
+      <c r="AB27" s="500"/>
+      <c r="AC27" s="500"/>
+      <c r="AD27" s="500"/>
+      <c r="AE27" s="500"/>
+      <c r="AF27" s="500"/>
+      <c r="AG27" s="501"/>
     </row>
     <row r="28" spans="3:33" ht="15" customHeight="1">
       <c r="C28" s="280" t="s">
@@ -8698,7 +8714,7 @@
       <c r="P31" s="304">
         <v>46374</v>
       </c>
-      <c r="Q31" s="305">
+      <c r="Q31" s="555">
         <v>46375</v>
       </c>
       <c r="R31" s="279"/>
@@ -9014,34 +9030,34 @@
       </c>
     </row>
     <row r="35" spans="3:34" ht="9.9499999999999993" customHeight="1">
-      <c r="C35" s="499"/>
-      <c r="D35" s="495"/>
-      <c r="E35" s="495"/>
-      <c r="F35" s="495"/>
-      <c r="G35" s="495"/>
-      <c r="H35" s="495"/>
-      <c r="I35" s="496"/>
-      <c r="K35" s="499"/>
-      <c r="L35" s="495"/>
-      <c r="M35" s="495"/>
-      <c r="N35" s="495"/>
-      <c r="O35" s="495"/>
-      <c r="P35" s="495"/>
-      <c r="Q35" s="496"/>
-      <c r="S35" s="499"/>
-      <c r="T35" s="495"/>
-      <c r="U35" s="495"/>
-      <c r="V35" s="495"/>
-      <c r="W35" s="495"/>
-      <c r="X35" s="495"/>
-      <c r="Y35" s="496"/>
-      <c r="AA35" s="499"/>
-      <c r="AB35" s="495"/>
-      <c r="AC35" s="495"/>
-      <c r="AD35" s="495"/>
-      <c r="AE35" s="495"/>
-      <c r="AF35" s="495"/>
-      <c r="AG35" s="496"/>
+      <c r="C35" s="502"/>
+      <c r="D35" s="497"/>
+      <c r="E35" s="497"/>
+      <c r="F35" s="497"/>
+      <c r="G35" s="497"/>
+      <c r="H35" s="497"/>
+      <c r="I35" s="498"/>
+      <c r="K35" s="502"/>
+      <c r="L35" s="497"/>
+      <c r="M35" s="497"/>
+      <c r="N35" s="497"/>
+      <c r="O35" s="497"/>
+      <c r="P35" s="497"/>
+      <c r="Q35" s="498"/>
+      <c r="S35" s="502"/>
+      <c r="T35" s="497"/>
+      <c r="U35" s="497"/>
+      <c r="V35" s="497"/>
+      <c r="W35" s="497"/>
+      <c r="X35" s="497"/>
+      <c r="Y35" s="498"/>
+      <c r="AA35" s="502"/>
+      <c r="AB35" s="497"/>
+      <c r="AC35" s="497"/>
+      <c r="AD35" s="497"/>
+      <c r="AE35" s="497"/>
+      <c r="AF35" s="497"/>
+      <c r="AG35" s="498"/>
     </row>
     <row r="36" spans="3:34" ht="15.75">
       <c r="C36" s="327"/>
@@ -9240,7 +9256,7 @@
       <c r="H40" s="327"/>
       <c r="I40" s="327"/>
       <c r="J40" s="328"/>
-      <c r="K40" s="347">
+      <c r="K40" s="330">
         <v>19</v>
       </c>
       <c r="L40" s="277" t="s">
@@ -9506,45 +9522,45 @@
       <c r="AH46" s="347"/>
     </row>
     <row r="47" spans="3:34" ht="15" customHeight="1">
-      <c r="C47" s="492">
+      <c r="C47" s="499">
         <v>46447</v>
       </c>
-      <c r="D47" s="493"/>
-      <c r="E47" s="493"/>
-      <c r="F47" s="493"/>
-      <c r="G47" s="493"/>
-      <c r="H47" s="493"/>
-      <c r="I47" s="494"/>
+      <c r="D47" s="500"/>
+      <c r="E47" s="500"/>
+      <c r="F47" s="500"/>
+      <c r="G47" s="500"/>
+      <c r="H47" s="500"/>
+      <c r="I47" s="501"/>
       <c r="J47" s="279"/>
-      <c r="K47" s="492">
+      <c r="K47" s="499">
         <v>46478</v>
       </c>
-      <c r="L47" s="493"/>
-      <c r="M47" s="493"/>
-      <c r="N47" s="493"/>
-      <c r="O47" s="493"/>
-      <c r="P47" s="493"/>
-      <c r="Q47" s="494"/>
+      <c r="L47" s="500"/>
+      <c r="M47" s="500"/>
+      <c r="N47" s="500"/>
+      <c r="O47" s="500"/>
+      <c r="P47" s="500"/>
+      <c r="Q47" s="501"/>
       <c r="R47" s="279"/>
-      <c r="S47" s="492">
+      <c r="S47" s="499">
         <v>46508</v>
       </c>
-      <c r="T47" s="493"/>
-      <c r="U47" s="493"/>
-      <c r="V47" s="493"/>
-      <c r="W47" s="493"/>
-      <c r="X47" s="493"/>
-      <c r="Y47" s="494"/>
+      <c r="T47" s="500"/>
+      <c r="U47" s="500"/>
+      <c r="V47" s="500"/>
+      <c r="W47" s="500"/>
+      <c r="X47" s="500"/>
+      <c r="Y47" s="501"/>
       <c r="Z47" s="279"/>
-      <c r="AA47" s="492">
+      <c r="AA47" s="499">
         <v>46539</v>
       </c>
-      <c r="AB47" s="493"/>
-      <c r="AC47" s="493"/>
-      <c r="AD47" s="493"/>
-      <c r="AE47" s="493"/>
-      <c r="AF47" s="493"/>
-      <c r="AG47" s="494"/>
+      <c r="AB47" s="500"/>
+      <c r="AC47" s="500"/>
+      <c r="AD47" s="500"/>
+      <c r="AE47" s="500"/>
+      <c r="AF47" s="500"/>
+      <c r="AG47" s="501"/>
     </row>
     <row r="48" spans="3:34" ht="15" customHeight="1">
       <c r="C48" s="349" t="s">
@@ -9798,7 +9814,7 @@
       <c r="AA50" s="461">
         <v>46544</v>
       </c>
-      <c r="AB50" s="303">
+      <c r="AB50" s="304">
         <v>46545</v>
       </c>
       <c r="AC50" s="300">
@@ -9813,7 +9829,7 @@
       <c r="AF50" s="300">
         <v>46549</v>
       </c>
-      <c r="AG50" s="307">
+      <c r="AG50" s="305">
         <v>46550</v>
       </c>
     </row>
@@ -9887,7 +9903,7 @@
       <c r="AA51" s="299">
         <v>46551</v>
       </c>
-      <c r="AB51" s="304">
+      <c r="AB51" s="303">
         <v>46552</v>
       </c>
       <c r="AC51" s="304">
@@ -9902,7 +9918,7 @@
       <c r="AF51" s="304">
         <v>46556</v>
       </c>
-      <c r="AG51" s="301">
+      <c r="AG51" s="556">
         <v>46557</v>
       </c>
     </row>
@@ -10174,34 +10190,34 @@
       </c>
     </row>
     <row r="55" spans="1:35" ht="9.9499999999999993" customHeight="1">
-      <c r="C55" s="500"/>
-      <c r="D55" s="501"/>
-      <c r="E55" s="497"/>
-      <c r="F55" s="502"/>
-      <c r="G55" s="501"/>
-      <c r="H55" s="497"/>
-      <c r="I55" s="498"/>
-      <c r="K55" s="500"/>
-      <c r="L55" s="501"/>
-      <c r="M55" s="497"/>
-      <c r="N55" s="502"/>
-      <c r="O55" s="501"/>
-      <c r="P55" s="497"/>
-      <c r="Q55" s="498"/>
-      <c r="S55" s="500"/>
-      <c r="T55" s="501"/>
-      <c r="U55" s="497"/>
-      <c r="V55" s="502"/>
-      <c r="W55" s="501"/>
-      <c r="X55" s="497"/>
-      <c r="Y55" s="498"/>
-      <c r="AA55" s="500"/>
-      <c r="AB55" s="501"/>
-      <c r="AC55" s="497"/>
-      <c r="AD55" s="502"/>
-      <c r="AE55" s="501"/>
-      <c r="AF55" s="497"/>
-      <c r="AG55" s="498"/>
+      <c r="C55" s="496"/>
+      <c r="D55" s="493"/>
+      <c r="E55" s="491"/>
+      <c r="F55" s="492"/>
+      <c r="G55" s="493"/>
+      <c r="H55" s="491"/>
+      <c r="I55" s="494"/>
+      <c r="K55" s="496"/>
+      <c r="L55" s="493"/>
+      <c r="M55" s="491"/>
+      <c r="N55" s="492"/>
+      <c r="O55" s="493"/>
+      <c r="P55" s="491"/>
+      <c r="Q55" s="494"/>
+      <c r="S55" s="496"/>
+      <c r="T55" s="493"/>
+      <c r="U55" s="491"/>
+      <c r="V55" s="492"/>
+      <c r="W55" s="493"/>
+      <c r="X55" s="491"/>
+      <c r="Y55" s="494"/>
+      <c r="AA55" s="496"/>
+      <c r="AB55" s="493"/>
+      <c r="AC55" s="491"/>
+      <c r="AD55" s="492"/>
+      <c r="AE55" s="493"/>
+      <c r="AF55" s="491"/>
+      <c r="AG55" s="494"/>
     </row>
     <row r="56" spans="1:35" ht="15.75">
       <c r="A56" s="347"/>
@@ -10332,7 +10348,7 @@
       <c r="X58" s="327"/>
       <c r="Y58" s="327"/>
       <c r="Z58" s="328"/>
-      <c r="AA58" s="347">
+      <c r="AA58" s="558">
         <v>6</v>
       </c>
       <c r="AB58" s="331" t="s">
@@ -10386,7 +10402,7 @@
       <c r="Y59" s="327"/>
       <c r="Z59" s="328"/>
       <c r="AA59" s="329">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AB59" s="327" t="s">
         <v>196</v>
@@ -10434,11 +10450,11 @@
       <c r="X60" s="327"/>
       <c r="Y60" s="327"/>
       <c r="Z60" s="328"/>
-      <c r="AA60" s="333">
-        <v>12</v>
-      </c>
-      <c r="AB60" s="327" t="s">
-        <v>198</v>
+      <c r="AA60" s="557">
+        <v>19</v>
+      </c>
+      <c r="AB60" s="277" t="s">
+        <v>383</v>
       </c>
       <c r="AC60" s="327"/>
       <c r="AD60" s="327"/>
@@ -10481,7 +10497,7 @@
         <v>240</v>
       </c>
       <c r="AB61" s="327" t="s">
-        <v>383</v>
+        <v>195</v>
       </c>
       <c r="AC61" s="327"/>
       <c r="AD61" s="327"/>
@@ -10522,8 +10538,6 @@
       <c r="X62" s="327"/>
       <c r="Y62" s="327"/>
       <c r="Z62" s="328"/>
-      <c r="AA62" s="327"/>
-      <c r="AB62" s="327"/>
       <c r="AC62" s="327"/>
       <c r="AD62" s="327"/>
       <c r="AE62" s="327"/>
@@ -10583,21 +10597,21 @@
       <c r="O64" s="360"/>
       <c r="P64" s="360"/>
       <c r="Q64" s="360"/>
-      <c r="S64" s="503"/>
-      <c r="T64" s="503"/>
-      <c r="U64" s="503"/>
-      <c r="V64" s="503"/>
-      <c r="W64" s="503"/>
-      <c r="X64" s="503"/>
-      <c r="Y64" s="503"/>
-      <c r="Z64" s="503"/>
-      <c r="AA64" s="503"/>
-      <c r="AB64" s="503"/>
-      <c r="AC64" s="503"/>
-      <c r="AD64" s="503"/>
-      <c r="AE64" s="503"/>
-      <c r="AF64" s="503"/>
-      <c r="AG64" s="503"/>
+      <c r="S64" s="495"/>
+      <c r="T64" s="495"/>
+      <c r="U64" s="495"/>
+      <c r="V64" s="495"/>
+      <c r="W64" s="495"/>
+      <c r="X64" s="495"/>
+      <c r="Y64" s="495"/>
+      <c r="Z64" s="495"/>
+      <c r="AA64" s="495"/>
+      <c r="AB64" s="495"/>
+      <c r="AC64" s="495"/>
+      <c r="AD64" s="495"/>
+      <c r="AE64" s="495"/>
+      <c r="AF64" s="495"/>
+      <c r="AG64" s="495"/>
     </row>
     <row r="65" spans="3:35" ht="14.25" customHeight="1">
       <c r="C65" s="362"/>
@@ -10617,21 +10631,21 @@
       <c r="O65" s="363"/>
       <c r="P65" s="363"/>
       <c r="Q65" s="363"/>
-      <c r="S65" s="503"/>
-      <c r="T65" s="503"/>
-      <c r="U65" s="503"/>
-      <c r="V65" s="503"/>
-      <c r="W65" s="503"/>
-      <c r="X65" s="503"/>
-      <c r="Y65" s="503"/>
-      <c r="Z65" s="503"/>
-      <c r="AA65" s="503"/>
-      <c r="AB65" s="503"/>
-      <c r="AC65" s="503"/>
-      <c r="AD65" s="503"/>
-      <c r="AE65" s="503"/>
-      <c r="AF65" s="503"/>
-      <c r="AG65" s="503"/>
+      <c r="S65" s="495"/>
+      <c r="T65" s="495"/>
+      <c r="U65" s="495"/>
+      <c r="V65" s="495"/>
+      <c r="W65" s="495"/>
+      <c r="X65" s="495"/>
+      <c r="Y65" s="495"/>
+      <c r="Z65" s="495"/>
+      <c r="AA65" s="495"/>
+      <c r="AB65" s="495"/>
+      <c r="AC65" s="495"/>
+      <c r="AD65" s="495"/>
+      <c r="AE65" s="495"/>
+      <c r="AF65" s="495"/>
+      <c r="AG65" s="495"/>
     </row>
     <row r="66" spans="3:35" ht="14.25" customHeight="1">
       <c r="C66" s="364"/>
@@ -10903,21 +10917,27 @@
     <row r="125" hidden="1"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AC55:AE55"/>
-    <mergeCell ref="AF55:AG55"/>
-    <mergeCell ref="S64:AG64"/>
-    <mergeCell ref="S65:V65"/>
-    <mergeCell ref="W65:AG65"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="S55:T55"/>
-    <mergeCell ref="U55:W55"/>
-    <mergeCell ref="X55:Y55"/>
-    <mergeCell ref="AA55:AB55"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="M55:O55"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="S6:Y6"/>
+    <mergeCell ref="AA6:AG6"/>
+    <mergeCell ref="AC14:AE14"/>
+    <mergeCell ref="AF14:AG14"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="S27:Y27"/>
+    <mergeCell ref="AA27:AG27"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:O14"/>
     <mergeCell ref="AC35:AE35"/>
     <mergeCell ref="AF35:AG35"/>
     <mergeCell ref="C47:I47"/>
@@ -10934,27 +10954,21 @@
     <mergeCell ref="H35:I35"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="M35:O35"/>
-    <mergeCell ref="AC14:AE14"/>
-    <mergeCell ref="AF14:AG14"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="S27:Y27"/>
-    <mergeCell ref="AA27:AG27"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="K6:Q6"/>
-    <mergeCell ref="S6:Y6"/>
-    <mergeCell ref="AA6:AG6"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="M55:O55"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="S55:T55"/>
+    <mergeCell ref="U55:W55"/>
+    <mergeCell ref="X55:Y55"/>
+    <mergeCell ref="AA55:AB55"/>
+    <mergeCell ref="AC55:AE55"/>
+    <mergeCell ref="AF55:AG55"/>
+    <mergeCell ref="S64:AG64"/>
+    <mergeCell ref="S65:V65"/>
+    <mergeCell ref="W65:AG65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11221,365 +11235,365 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:89 16342:16384" ht="34.5" customHeight="1">
-      <c r="A1" s="508" t="s">
+      <c r="A1" s="554" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="508"/>
-      <c r="C1" s="508"/>
-      <c r="D1" s="508"/>
-      <c r="E1" s="508"/>
-      <c r="F1" s="508"/>
-      <c r="G1" s="508"/>
-      <c r="H1" s="508"/>
-      <c r="I1" s="508"/>
-      <c r="J1" s="508"/>
-      <c r="K1" s="508"/>
-      <c r="L1" s="508"/>
-      <c r="M1" s="508"/>
-      <c r="N1" s="508"/>
-      <c r="O1" s="508"/>
-      <c r="P1" s="508"/>
-      <c r="Q1" s="508"/>
-      <c r="R1" s="508"/>
-      <c r="S1" s="508"/>
-      <c r="T1" s="508"/>
-      <c r="U1" s="508"/>
-      <c r="V1" s="508"/>
-      <c r="W1" s="508"/>
-      <c r="X1" s="508"/>
-      <c r="Y1" s="508"/>
-      <c r="Z1" s="508"/>
-      <c r="AA1" s="508"/>
-      <c r="AB1" s="508"/>
-      <c r="AC1" s="508"/>
-      <c r="AD1" s="508"/>
-      <c r="AE1" s="508"/>
-      <c r="AF1" s="508"/>
-      <c r="AG1" s="508"/>
-      <c r="AH1" s="508"/>
-      <c r="AI1" s="508"/>
-      <c r="AJ1" s="508"/>
-      <c r="AK1" s="508"/>
-      <c r="AL1" s="508"/>
-      <c r="AM1" s="508"/>
-      <c r="AN1" s="508"/>
-      <c r="AO1" s="508"/>
-      <c r="AP1" s="508"/>
-      <c r="AQ1" s="508"/>
-      <c r="AR1" s="508"/>
-      <c r="AS1" s="508"/>
-      <c r="AT1" s="508"/>
-      <c r="AU1" s="508"/>
-      <c r="AV1" s="508"/>
-      <c r="AW1" s="508"/>
-      <c r="AX1" s="508"/>
-      <c r="AY1" s="508"/>
-      <c r="AZ1" s="508"/>
-      <c r="BA1" s="508"/>
-      <c r="BB1" s="508"/>
-      <c r="BC1" s="508"/>
-      <c r="BD1" s="508"/>
-      <c r="BE1" s="508"/>
-      <c r="BF1" s="508"/>
-      <c r="BG1" s="508"/>
-      <c r="BH1" s="508"/>
-      <c r="BI1" s="508"/>
-      <c r="BJ1" s="508"/>
-      <c r="BK1" s="508"/>
-      <c r="BL1" s="508"/>
-      <c r="BM1" s="508"/>
-      <c r="BN1" s="508"/>
-      <c r="BO1" s="508"/>
-      <c r="BP1" s="508"/>
-      <c r="BQ1" s="508"/>
-      <c r="BR1" s="508"/>
-      <c r="BS1" s="508"/>
-      <c r="BT1" s="508"/>
-      <c r="BU1" s="508"/>
-      <c r="BV1" s="508"/>
-      <c r="BW1" s="508"/>
-      <c r="BX1" s="508"/>
-      <c r="BY1" s="508"/>
-      <c r="BZ1" s="508"/>
-      <c r="CA1" s="508"/>
-      <c r="CB1" s="508"/>
-      <c r="CC1" s="508"/>
-      <c r="CD1" s="508"/>
-      <c r="CE1" s="508"/>
-      <c r="CF1" s="508"/>
-      <c r="CG1" s="508"/>
-      <c r="CH1" s="508"/>
-      <c r="CI1" s="508"/>
-      <c r="CJ1" s="508"/>
-      <c r="CK1" s="508"/>
+      <c r="B1" s="554"/>
+      <c r="C1" s="554"/>
+      <c r="D1" s="554"/>
+      <c r="E1" s="554"/>
+      <c r="F1" s="554"/>
+      <c r="G1" s="554"/>
+      <c r="H1" s="554"/>
+      <c r="I1" s="554"/>
+      <c r="J1" s="554"/>
+      <c r="K1" s="554"/>
+      <c r="L1" s="554"/>
+      <c r="M1" s="554"/>
+      <c r="N1" s="554"/>
+      <c r="O1" s="554"/>
+      <c r="P1" s="554"/>
+      <c r="Q1" s="554"/>
+      <c r="R1" s="554"/>
+      <c r="S1" s="554"/>
+      <c r="T1" s="554"/>
+      <c r="U1" s="554"/>
+      <c r="V1" s="554"/>
+      <c r="W1" s="554"/>
+      <c r="X1" s="554"/>
+      <c r="Y1" s="554"/>
+      <c r="Z1" s="554"/>
+      <c r="AA1" s="554"/>
+      <c r="AB1" s="554"/>
+      <c r="AC1" s="554"/>
+      <c r="AD1" s="554"/>
+      <c r="AE1" s="554"/>
+      <c r="AF1" s="554"/>
+      <c r="AG1" s="554"/>
+      <c r="AH1" s="554"/>
+      <c r="AI1" s="554"/>
+      <c r="AJ1" s="554"/>
+      <c r="AK1" s="554"/>
+      <c r="AL1" s="554"/>
+      <c r="AM1" s="554"/>
+      <c r="AN1" s="554"/>
+      <c r="AO1" s="554"/>
+      <c r="AP1" s="554"/>
+      <c r="AQ1" s="554"/>
+      <c r="AR1" s="554"/>
+      <c r="AS1" s="554"/>
+      <c r="AT1" s="554"/>
+      <c r="AU1" s="554"/>
+      <c r="AV1" s="554"/>
+      <c r="AW1" s="554"/>
+      <c r="AX1" s="554"/>
+      <c r="AY1" s="554"/>
+      <c r="AZ1" s="554"/>
+      <c r="BA1" s="554"/>
+      <c r="BB1" s="554"/>
+      <c r="BC1" s="554"/>
+      <c r="BD1" s="554"/>
+      <c r="BE1" s="554"/>
+      <c r="BF1" s="554"/>
+      <c r="BG1" s="554"/>
+      <c r="BH1" s="554"/>
+      <c r="BI1" s="554"/>
+      <c r="BJ1" s="554"/>
+      <c r="BK1" s="554"/>
+      <c r="BL1" s="554"/>
+      <c r="BM1" s="554"/>
+      <c r="BN1" s="554"/>
+      <c r="BO1" s="554"/>
+      <c r="BP1" s="554"/>
+      <c r="BQ1" s="554"/>
+      <c r="BR1" s="554"/>
+      <c r="BS1" s="554"/>
+      <c r="BT1" s="554"/>
+      <c r="BU1" s="554"/>
+      <c r="BV1" s="554"/>
+      <c r="BW1" s="554"/>
+      <c r="BX1" s="554"/>
+      <c r="BY1" s="554"/>
+      <c r="BZ1" s="554"/>
+      <c r="CA1" s="554"/>
+      <c r="CB1" s="554"/>
+      <c r="CC1" s="554"/>
+      <c r="CD1" s="554"/>
+      <c r="CE1" s="554"/>
+      <c r="CF1" s="554"/>
+      <c r="CG1" s="554"/>
+      <c r="CH1" s="554"/>
+      <c r="CI1" s="554"/>
+      <c r="CJ1" s="554"/>
+      <c r="CK1" s="554"/>
     </row>
     <row r="3" spans="1:89 16342:16384" s="1" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A3" s="509" t="s">
+      <c r="A3" s="540" t="s">
         <v>275</v>
       </c>
-      <c r="B3" s="510"/>
-      <c r="C3" s="510"/>
-      <c r="D3" s="510"/>
-      <c r="E3" s="510"/>
-      <c r="F3" s="510"/>
-      <c r="G3" s="510"/>
-      <c r="H3" s="510"/>
-      <c r="I3" s="510"/>
-      <c r="J3" s="510"/>
-      <c r="K3" s="510"/>
-      <c r="L3" s="510"/>
-      <c r="M3" s="510"/>
-      <c r="N3" s="510"/>
-      <c r="P3" s="511" t="s">
+      <c r="B3" s="541"/>
+      <c r="C3" s="541"/>
+      <c r="D3" s="541"/>
+      <c r="E3" s="541"/>
+      <c r="F3" s="541"/>
+      <c r="G3" s="541"/>
+      <c r="H3" s="541"/>
+      <c r="I3" s="541"/>
+      <c r="J3" s="541"/>
+      <c r="K3" s="541"/>
+      <c r="L3" s="541"/>
+      <c r="M3" s="541"/>
+      <c r="N3" s="541"/>
+      <c r="P3" s="544" t="s">
         <v>276</v>
       </c>
-      <c r="Q3" s="512"/>
-      <c r="R3" s="512"/>
-      <c r="S3" s="512"/>
-      <c r="T3" s="512"/>
-      <c r="U3" s="512"/>
-      <c r="V3" s="512"/>
-      <c r="W3" s="512"/>
-      <c r="X3" s="512"/>
-      <c r="Y3" s="512"/>
-      <c r="Z3" s="512"/>
-      <c r="AA3" s="512"/>
-      <c r="AB3" s="512"/>
-      <c r="AC3" s="512"/>
-      <c r="AE3" s="511" t="s">
+      <c r="Q3" s="545"/>
+      <c r="R3" s="545"/>
+      <c r="S3" s="545"/>
+      <c r="T3" s="545"/>
+      <c r="U3" s="545"/>
+      <c r="V3" s="545"/>
+      <c r="W3" s="545"/>
+      <c r="X3" s="545"/>
+      <c r="Y3" s="545"/>
+      <c r="Z3" s="545"/>
+      <c r="AA3" s="545"/>
+      <c r="AB3" s="545"/>
+      <c r="AC3" s="545"/>
+      <c r="AE3" s="544" t="s">
         <v>277</v>
       </c>
-      <c r="AF3" s="512"/>
-      <c r="AG3" s="512"/>
-      <c r="AH3" s="512"/>
-      <c r="AI3" s="512"/>
-      <c r="AJ3" s="512"/>
-      <c r="AK3" s="512"/>
-      <c r="AL3" s="512"/>
-      <c r="AM3" s="512"/>
-      <c r="AN3" s="512"/>
-      <c r="AO3" s="512"/>
-      <c r="AP3" s="512"/>
-      <c r="AQ3" s="512"/>
-      <c r="AR3" s="512"/>
-      <c r="AT3" s="511" t="s">
+      <c r="AF3" s="545"/>
+      <c r="AG3" s="545"/>
+      <c r="AH3" s="545"/>
+      <c r="AI3" s="545"/>
+      <c r="AJ3" s="545"/>
+      <c r="AK3" s="545"/>
+      <c r="AL3" s="545"/>
+      <c r="AM3" s="545"/>
+      <c r="AN3" s="545"/>
+      <c r="AO3" s="545"/>
+      <c r="AP3" s="545"/>
+      <c r="AQ3" s="545"/>
+      <c r="AR3" s="545"/>
+      <c r="AT3" s="544" t="s">
         <v>278</v>
       </c>
-      <c r="AU3" s="512"/>
-      <c r="AV3" s="512"/>
-      <c r="AW3" s="512"/>
-      <c r="AX3" s="512"/>
-      <c r="AY3" s="512"/>
-      <c r="AZ3" s="512"/>
-      <c r="BA3" s="512"/>
-      <c r="BB3" s="512"/>
-      <c r="BC3" s="512"/>
-      <c r="BD3" s="512"/>
-      <c r="BE3" s="512"/>
-      <c r="BF3" s="512"/>
-      <c r="BG3" s="512"/>
-      <c r="BI3" s="511" t="s">
+      <c r="AU3" s="545"/>
+      <c r="AV3" s="545"/>
+      <c r="AW3" s="545"/>
+      <c r="AX3" s="545"/>
+      <c r="AY3" s="545"/>
+      <c r="AZ3" s="545"/>
+      <c r="BA3" s="545"/>
+      <c r="BB3" s="545"/>
+      <c r="BC3" s="545"/>
+      <c r="BD3" s="545"/>
+      <c r="BE3" s="545"/>
+      <c r="BF3" s="545"/>
+      <c r="BG3" s="545"/>
+      <c r="BI3" s="544" t="s">
         <v>279</v>
       </c>
-      <c r="BJ3" s="512"/>
-      <c r="BK3" s="512"/>
-      <c r="BL3" s="512"/>
-      <c r="BM3" s="512"/>
-      <c r="BN3" s="512"/>
-      <c r="BO3" s="512"/>
-      <c r="BP3" s="512"/>
-      <c r="BQ3" s="512"/>
-      <c r="BR3" s="512"/>
-      <c r="BS3" s="512"/>
-      <c r="BT3" s="512"/>
-      <c r="BU3" s="512"/>
-      <c r="BV3" s="512"/>
-      <c r="BX3" s="511" t="s">
+      <c r="BJ3" s="545"/>
+      <c r="BK3" s="545"/>
+      <c r="BL3" s="545"/>
+      <c r="BM3" s="545"/>
+      <c r="BN3" s="545"/>
+      <c r="BO3" s="545"/>
+      <c r="BP3" s="545"/>
+      <c r="BQ3" s="545"/>
+      <c r="BR3" s="545"/>
+      <c r="BS3" s="545"/>
+      <c r="BT3" s="545"/>
+      <c r="BU3" s="545"/>
+      <c r="BV3" s="545"/>
+      <c r="BX3" s="544" t="s">
         <v>280</v>
       </c>
-      <c r="BY3" s="512"/>
-      <c r="BZ3" s="512"/>
-      <c r="CA3" s="512"/>
-      <c r="CB3" s="512"/>
-      <c r="CC3" s="512"/>
-      <c r="CD3" s="512"/>
-      <c r="CE3" s="512"/>
-      <c r="CF3" s="512"/>
-      <c r="CG3" s="512"/>
-      <c r="CH3" s="512"/>
-      <c r="CI3" s="512"/>
-      <c r="CJ3" s="512"/>
-      <c r="CK3" s="512"/>
+      <c r="BY3" s="545"/>
+      <c r="BZ3" s="545"/>
+      <c r="CA3" s="545"/>
+      <c r="CB3" s="545"/>
+      <c r="CC3" s="545"/>
+      <c r="CD3" s="545"/>
+      <c r="CE3" s="545"/>
+      <c r="CF3" s="545"/>
+      <c r="CG3" s="545"/>
+      <c r="CH3" s="545"/>
+      <c r="CI3" s="545"/>
+      <c r="CJ3" s="545"/>
+      <c r="CK3" s="545"/>
     </row>
     <row r="4" spans="1:89 16342:16384" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="513" t="s">
+      <c r="A4" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="B4" s="514"/>
-      <c r="C4" s="513" t="s">
+      <c r="B4" s="530"/>
+      <c r="C4" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="515"/>
-      <c r="E4" s="513" t="s">
+      <c r="D4" s="526"/>
+      <c r="E4" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="516"/>
-      <c r="G4" s="513" t="s">
+      <c r="F4" s="527"/>
+      <c r="G4" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="515"/>
-      <c r="I4" s="513" t="s">
+      <c r="H4" s="526"/>
+      <c r="I4" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="515"/>
-      <c r="K4" s="517" t="s">
+      <c r="J4" s="526"/>
+      <c r="K4" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="518"/>
-      <c r="M4" s="513" t="s">
+      <c r="L4" s="529"/>
+      <c r="M4" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="514"/>
-      <c r="P4" s="513" t="s">
+      <c r="N4" s="530"/>
+      <c r="P4" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="Q4" s="514"/>
-      <c r="R4" s="513" t="s">
+      <c r="Q4" s="530"/>
+      <c r="R4" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="S4" s="515"/>
-      <c r="T4" s="513" t="s">
+      <c r="S4" s="526"/>
+      <c r="T4" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="U4" s="516"/>
-      <c r="V4" s="513" t="s">
+      <c r="U4" s="527"/>
+      <c r="V4" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="W4" s="515"/>
-      <c r="X4" s="513" t="s">
+      <c r="W4" s="526"/>
+      <c r="X4" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="515"/>
-      <c r="Z4" s="517" t="s">
+      <c r="Y4" s="526"/>
+      <c r="Z4" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="AA4" s="518"/>
-      <c r="AB4" s="513" t="s">
+      <c r="AA4" s="529"/>
+      <c r="AB4" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="AC4" s="514"/>
-      <c r="AE4" s="513" t="s">
+      <c r="AC4" s="530"/>
+      <c r="AE4" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="AF4" s="514"/>
-      <c r="AG4" s="513" t="s">
+      <c r="AF4" s="530"/>
+      <c r="AG4" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="AH4" s="515"/>
-      <c r="AI4" s="513" t="s">
+      <c r="AH4" s="526"/>
+      <c r="AI4" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="AJ4" s="516"/>
-      <c r="AK4" s="513" t="s">
+      <c r="AJ4" s="527"/>
+      <c r="AK4" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="AL4" s="515"/>
-      <c r="AM4" s="513" t="s">
+      <c r="AL4" s="526"/>
+      <c r="AM4" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="AN4" s="515"/>
-      <c r="AO4" s="517" t="s">
+      <c r="AN4" s="526"/>
+      <c r="AO4" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="AP4" s="518"/>
-      <c r="AQ4" s="513" t="s">
+      <c r="AP4" s="529"/>
+      <c r="AQ4" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="AR4" s="514"/>
-      <c r="AT4" s="513" t="s">
+      <c r="AR4" s="530"/>
+      <c r="AT4" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="AU4" s="514"/>
-      <c r="AV4" s="513" t="s">
+      <c r="AU4" s="530"/>
+      <c r="AV4" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="AW4" s="515"/>
-      <c r="AX4" s="513" t="s">
+      <c r="AW4" s="526"/>
+      <c r="AX4" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="AY4" s="516"/>
-      <c r="AZ4" s="513" t="s">
+      <c r="AY4" s="527"/>
+      <c r="AZ4" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="BA4" s="515"/>
-      <c r="BB4" s="513" t="s">
+      <c r="BA4" s="526"/>
+      <c r="BB4" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="BC4" s="515"/>
-      <c r="BD4" s="517" t="s">
+      <c r="BC4" s="526"/>
+      <c r="BD4" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="BE4" s="518"/>
-      <c r="BF4" s="513" t="s">
+      <c r="BE4" s="529"/>
+      <c r="BF4" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="BG4" s="514"/>
-      <c r="BI4" s="513" t="s">
+      <c r="BG4" s="530"/>
+      <c r="BI4" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="BJ4" s="514"/>
-      <c r="BK4" s="513" t="s">
+      <c r="BJ4" s="530"/>
+      <c r="BK4" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="BL4" s="515"/>
-      <c r="BM4" s="513" t="s">
+      <c r="BL4" s="526"/>
+      <c r="BM4" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="BN4" s="516"/>
-      <c r="BO4" s="513" t="s">
+      <c r="BN4" s="527"/>
+      <c r="BO4" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="BP4" s="515"/>
-      <c r="BQ4" s="513" t="s">
+      <c r="BP4" s="526"/>
+      <c r="BQ4" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="BR4" s="515"/>
-      <c r="BS4" s="517" t="s">
+      <c r="BR4" s="526"/>
+      <c r="BS4" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="BT4" s="518"/>
-      <c r="BU4" s="513" t="s">
+      <c r="BT4" s="529"/>
+      <c r="BU4" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="BV4" s="514"/>
-      <c r="BX4" s="513" t="s">
+      <c r="BV4" s="530"/>
+      <c r="BX4" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="BY4" s="514"/>
-      <c r="BZ4" s="513" t="s">
+      <c r="BY4" s="530"/>
+      <c r="BZ4" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="CA4" s="515"/>
-      <c r="CB4" s="513" t="s">
+      <c r="CA4" s="526"/>
+      <c r="CB4" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="CC4" s="516"/>
-      <c r="CD4" s="513" t="s">
+      <c r="CC4" s="527"/>
+      <c r="CD4" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="CE4" s="515"/>
-      <c r="CF4" s="513" t="s">
+      <c r="CE4" s="526"/>
+      <c r="CF4" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="CG4" s="515"/>
-      <c r="CH4" s="517" t="s">
+      <c r="CG4" s="526"/>
+      <c r="CH4" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="CI4" s="518"/>
-      <c r="CJ4" s="513" t="s">
+      <c r="CI4" s="529"/>
+      <c r="CJ4" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="CK4" s="514"/>
+      <c r="CK4" s="530"/>
       <c r="XDN4" s="4"/>
       <c r="XDO4" s="4"/>
       <c r="XDP4" s="4"/>
@@ -11625,8 +11639,8 @@
       <c r="XFD4" s="4"/>
     </row>
     <row r="5" spans="1:89 16342:16384" s="1" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="519"/>
-      <c r="B5" s="520"/>
+      <c r="A5" s="552"/>
+      <c r="B5" s="553"/>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="7">
@@ -11697,18 +11711,18 @@
       <c r="AC5" s="20">
         <v>13</v>
       </c>
-      <c r="AE5" s="521"/>
-      <c r="AF5" s="522"/>
-      <c r="AG5" s="521"/>
-      <c r="AH5" s="523"/>
-      <c r="AI5" s="521"/>
-      <c r="AJ5" s="522"/>
-      <c r="AK5" s="521"/>
-      <c r="AL5" s="522"/>
-      <c r="AM5" s="524"/>
-      <c r="AN5" s="522"/>
-      <c r="AO5" s="524"/>
-      <c r="AP5" s="522"/>
+      <c r="AE5" s="533"/>
+      <c r="AF5" s="546"/>
+      <c r="AG5" s="533"/>
+      <c r="AH5" s="534"/>
+      <c r="AI5" s="533"/>
+      <c r="AJ5" s="546"/>
+      <c r="AK5" s="533"/>
+      <c r="AL5" s="546"/>
+      <c r="AM5" s="531"/>
+      <c r="AN5" s="546"/>
+      <c r="AO5" s="531"/>
+      <c r="AP5" s="546"/>
       <c r="AQ5" s="21">
         <v>1</v>
       </c>
@@ -11716,14 +11730,14 @@
         <v>10</v>
       </c>
       <c r="AS5" s="23"/>
-      <c r="AT5" s="525"/>
-      <c r="AU5" s="526"/>
-      <c r="AV5" s="525"/>
-      <c r="AW5" s="526"/>
-      <c r="AX5" s="525"/>
-      <c r="AY5" s="526"/>
-      <c r="AZ5" s="525"/>
-      <c r="BA5" s="526"/>
+      <c r="AT5" s="547"/>
+      <c r="AU5" s="548"/>
+      <c r="AV5" s="547"/>
+      <c r="AW5" s="548"/>
+      <c r="AX5" s="547"/>
+      <c r="AY5" s="548"/>
+      <c r="AZ5" s="547"/>
+      <c r="BA5" s="548"/>
       <c r="BB5" s="24">
         <v>1</v>
       </c>
@@ -12603,10 +12617,10 @@
       <c r="J9" s="40">
         <v>6</v>
       </c>
-      <c r="K9" s="524"/>
-      <c r="L9" s="527"/>
-      <c r="M9" s="528"/>
-      <c r="N9" s="529"/>
+      <c r="K9" s="531"/>
+      <c r="L9" s="532"/>
+      <c r="M9" s="550"/>
+      <c r="N9" s="551"/>
       <c r="P9" s="98">
         <v>28</v>
       </c>
@@ -12788,73 +12802,73 @@
       </c>
     </row>
     <row r="10" spans="1:89 16342:16384" s="1" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A10" s="530" t="s">
+      <c r="A10" s="518" t="s">
         <v>282</v>
       </c>
-      <c r="B10" s="530"/>
-      <c r="C10" s="530"/>
-      <c r="D10" s="530"/>
-      <c r="E10" s="530"/>
-      <c r="F10" s="530"/>
-      <c r="G10" s="530"/>
-      <c r="H10" s="530"/>
-      <c r="I10" s="530"/>
-      <c r="J10" s="530"/>
-      <c r="K10" s="530"/>
-      <c r="L10" s="530"/>
-      <c r="M10" s="530"/>
-      <c r="N10" s="530"/>
-      <c r="P10" s="530" t="s">
+      <c r="B10" s="518"/>
+      <c r="C10" s="518"/>
+      <c r="D10" s="518"/>
+      <c r="E10" s="518"/>
+      <c r="F10" s="518"/>
+      <c r="G10" s="518"/>
+      <c r="H10" s="518"/>
+      <c r="I10" s="518"/>
+      <c r="J10" s="518"/>
+      <c r="K10" s="518"/>
+      <c r="L10" s="518"/>
+      <c r="M10" s="518"/>
+      <c r="N10" s="518"/>
+      <c r="P10" s="518" t="s">
         <v>283</v>
       </c>
-      <c r="Q10" s="530"/>
-      <c r="R10" s="530"/>
-      <c r="S10" s="530"/>
-      <c r="T10" s="530"/>
-      <c r="U10" s="530"/>
-      <c r="V10" s="530"/>
-      <c r="W10" s="530"/>
-      <c r="X10" s="530"/>
-      <c r="Y10" s="530"/>
-      <c r="Z10" s="530"/>
-      <c r="AA10" s="530"/>
-      <c r="AB10" s="530"/>
-      <c r="AC10" s="530"/>
+      <c r="Q10" s="518"/>
+      <c r="R10" s="518"/>
+      <c r="S10" s="518"/>
+      <c r="T10" s="518"/>
+      <c r="U10" s="518"/>
+      <c r="V10" s="518"/>
+      <c r="W10" s="518"/>
+      <c r="X10" s="518"/>
+      <c r="Y10" s="518"/>
+      <c r="Z10" s="518"/>
+      <c r="AA10" s="518"/>
+      <c r="AB10" s="518"/>
+      <c r="AC10" s="518"/>
       <c r="AE10" s="43">
         <v>30</v>
       </c>
       <c r="AF10" s="54">
         <v>9</v>
       </c>
-      <c r="AG10" s="521"/>
-      <c r="AH10" s="522"/>
-      <c r="AI10" s="521"/>
-      <c r="AJ10" s="523"/>
-      <c r="AK10" s="521"/>
-      <c r="AL10" s="522"/>
-      <c r="AM10" s="521"/>
-      <c r="AN10" s="522"/>
-      <c r="AO10" s="521"/>
-      <c r="AP10" s="522"/>
-      <c r="AQ10" s="521"/>
-      <c r="AR10" s="522"/>
+      <c r="AG10" s="533"/>
+      <c r="AH10" s="546"/>
+      <c r="AI10" s="533"/>
+      <c r="AJ10" s="534"/>
+      <c r="AK10" s="533"/>
+      <c r="AL10" s="546"/>
+      <c r="AM10" s="533"/>
+      <c r="AN10" s="546"/>
+      <c r="AO10" s="533"/>
+      <c r="AP10" s="546"/>
+      <c r="AQ10" s="533"/>
+      <c r="AR10" s="546"/>
       <c r="AS10" s="23"/>
-      <c r="AT10" s="525"/>
-      <c r="AU10" s="526">
+      <c r="AT10" s="547"/>
+      <c r="AU10" s="548">
         <v>5</v>
       </c>
-      <c r="AV10" s="525"/>
-      <c r="AW10" s="526"/>
-      <c r="AX10" s="525"/>
-      <c r="AY10" s="526"/>
-      <c r="AZ10" s="525"/>
-      <c r="BA10" s="526"/>
-      <c r="BB10" s="525"/>
-      <c r="BC10" s="526"/>
-      <c r="BD10" s="525"/>
-      <c r="BE10" s="526"/>
-      <c r="BF10" s="525"/>
-      <c r="BG10" s="526"/>
+      <c r="AV10" s="547"/>
+      <c r="AW10" s="548"/>
+      <c r="AX10" s="547"/>
+      <c r="AY10" s="548"/>
+      <c r="AZ10" s="547"/>
+      <c r="BA10" s="548"/>
+      <c r="BB10" s="547"/>
+      <c r="BC10" s="548"/>
+      <c r="BD10" s="547"/>
+      <c r="BE10" s="548"/>
+      <c r="BF10" s="547"/>
+      <c r="BG10" s="548"/>
       <c r="BI10" s="30"/>
       <c r="BJ10" s="116"/>
       <c r="BK10" s="30"/>
@@ -12932,90 +12946,90 @@
       <c r="XFD10" s="3"/>
     </row>
     <row r="11" spans="1:89 16342:16384" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A11" s="531" t="s">
+      <c r="A11" s="549" t="s">
         <v>284</v>
       </c>
-      <c r="B11" s="531"/>
-      <c r="C11" s="531"/>
-      <c r="D11" s="531"/>
-      <c r="E11" s="531"/>
-      <c r="F11" s="531"/>
-      <c r="G11" s="531"/>
-      <c r="P11" s="532" t="s">
+      <c r="B11" s="549"/>
+      <c r="C11" s="549"/>
+      <c r="D11" s="549"/>
+      <c r="E11" s="549"/>
+      <c r="F11" s="549"/>
+      <c r="G11" s="549"/>
+      <c r="P11" s="508" t="s">
         <v>285</v>
       </c>
-      <c r="Q11" s="532"/>
-      <c r="R11" s="532"/>
-      <c r="S11" s="532"/>
-      <c r="T11" s="532"/>
-      <c r="U11" s="532"/>
-      <c r="V11" s="532"/>
-      <c r="W11" s="532"/>
-      <c r="AE11" s="533" t="s">
+      <c r="Q11" s="508"/>
+      <c r="R11" s="508"/>
+      <c r="S11" s="508"/>
+      <c r="T11" s="508"/>
+      <c r="U11" s="508"/>
+      <c r="V11" s="508"/>
+      <c r="W11" s="508"/>
+      <c r="AE11" s="535" t="s">
         <v>286</v>
       </c>
-      <c r="AF11" s="534"/>
-      <c r="AG11" s="534"/>
-      <c r="AH11" s="534"/>
-      <c r="AI11" s="534"/>
-      <c r="AJ11" s="534"/>
-      <c r="AK11" s="534"/>
-      <c r="AL11" s="534"/>
-      <c r="AM11" s="534"/>
-      <c r="AN11" s="534"/>
-      <c r="AO11" s="534"/>
-      <c r="AP11" s="534"/>
-      <c r="AQ11" s="534"/>
-      <c r="AR11" s="535"/>
+      <c r="AF11" s="536"/>
+      <c r="AG11" s="536"/>
+      <c r="AH11" s="536"/>
+      <c r="AI11" s="536"/>
+      <c r="AJ11" s="536"/>
+      <c r="AK11" s="536"/>
+      <c r="AL11" s="536"/>
+      <c r="AM11" s="536"/>
+      <c r="AN11" s="536"/>
+      <c r="AO11" s="536"/>
+      <c r="AP11" s="536"/>
+      <c r="AQ11" s="536"/>
+      <c r="AR11" s="537"/>
       <c r="AS11" s="23"/>
-      <c r="AT11" s="533" t="s">
+      <c r="AT11" s="535" t="s">
         <v>287</v>
       </c>
-      <c r="AU11" s="534"/>
-      <c r="AV11" s="534"/>
-      <c r="AW11" s="534"/>
-      <c r="AX11" s="534"/>
-      <c r="AY11" s="534"/>
-      <c r="AZ11" s="534"/>
-      <c r="BA11" s="534"/>
-      <c r="BB11" s="534"/>
-      <c r="BC11" s="534"/>
-      <c r="BD11" s="534"/>
-      <c r="BE11" s="534"/>
-      <c r="BF11" s="534"/>
-      <c r="BG11" s="535"/>
-      <c r="BI11" s="533" t="s">
+      <c r="AU11" s="536"/>
+      <c r="AV11" s="536"/>
+      <c r="AW11" s="536"/>
+      <c r="AX11" s="536"/>
+      <c r="AY11" s="536"/>
+      <c r="AZ11" s="536"/>
+      <c r="BA11" s="536"/>
+      <c r="BB11" s="536"/>
+      <c r="BC11" s="536"/>
+      <c r="BD11" s="536"/>
+      <c r="BE11" s="536"/>
+      <c r="BF11" s="536"/>
+      <c r="BG11" s="537"/>
+      <c r="BI11" s="535" t="s">
         <v>288</v>
       </c>
-      <c r="BJ11" s="534"/>
-      <c r="BK11" s="534"/>
-      <c r="BL11" s="534"/>
-      <c r="BM11" s="534"/>
-      <c r="BN11" s="534"/>
-      <c r="BO11" s="534"/>
-      <c r="BP11" s="534"/>
-      <c r="BQ11" s="534"/>
-      <c r="BR11" s="534"/>
-      <c r="BS11" s="534"/>
-      <c r="BT11" s="534"/>
-      <c r="BU11" s="534"/>
-      <c r="BV11" s="535"/>
-      <c r="BX11" s="533" t="s">
+      <c r="BJ11" s="536"/>
+      <c r="BK11" s="536"/>
+      <c r="BL11" s="536"/>
+      <c r="BM11" s="536"/>
+      <c r="BN11" s="536"/>
+      <c r="BO11" s="536"/>
+      <c r="BP11" s="536"/>
+      <c r="BQ11" s="536"/>
+      <c r="BR11" s="536"/>
+      <c r="BS11" s="536"/>
+      <c r="BT11" s="536"/>
+      <c r="BU11" s="536"/>
+      <c r="BV11" s="537"/>
+      <c r="BX11" s="535" t="s">
         <v>286</v>
       </c>
-      <c r="BY11" s="534"/>
-      <c r="BZ11" s="534"/>
-      <c r="CA11" s="534"/>
-      <c r="CB11" s="534"/>
-      <c r="CC11" s="534"/>
-      <c r="CD11" s="534"/>
-      <c r="CE11" s="534"/>
-      <c r="CF11" s="534"/>
-      <c r="CG11" s="534"/>
-      <c r="CH11" s="534"/>
-      <c r="CI11" s="534"/>
-      <c r="CJ11" s="534"/>
-      <c r="CK11" s="535"/>
+      <c r="BY11" s="536"/>
+      <c r="BZ11" s="536"/>
+      <c r="CA11" s="536"/>
+      <c r="CB11" s="536"/>
+      <c r="CC11" s="536"/>
+      <c r="CD11" s="536"/>
+      <c r="CE11" s="536"/>
+      <c r="CF11" s="536"/>
+      <c r="CG11" s="536"/>
+      <c r="CH11" s="536"/>
+      <c r="CI11" s="536"/>
+      <c r="CJ11" s="536"/>
+      <c r="CK11" s="537"/>
     </row>
     <row r="12" spans="1:89 16342:16384" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A12" s="127">
@@ -13053,49 +13067,49 @@
       <c r="AA12" s="134"/>
       <c r="AB12" s="134"/>
       <c r="AC12" s="134"/>
-      <c r="AE12" s="532" t="s">
+      <c r="AE12" s="508" t="s">
         <v>291</v>
       </c>
-      <c r="AF12" s="532"/>
-      <c r="AG12" s="532"/>
-      <c r="AH12" s="532"/>
-      <c r="AI12" s="532"/>
-      <c r="AJ12" s="532"/>
-      <c r="AK12" s="532"/>
-      <c r="AL12" s="532"/>
-      <c r="AM12" s="532"/>
-      <c r="AT12" s="532" t="s">
+      <c r="AF12" s="508"/>
+      <c r="AG12" s="508"/>
+      <c r="AH12" s="508"/>
+      <c r="AI12" s="508"/>
+      <c r="AJ12" s="508"/>
+      <c r="AK12" s="508"/>
+      <c r="AL12" s="508"/>
+      <c r="AM12" s="508"/>
+      <c r="AT12" s="508" t="s">
         <v>292</v>
       </c>
-      <c r="AU12" s="532"/>
-      <c r="AV12" s="532"/>
-      <c r="AW12" s="532"/>
-      <c r="AX12" s="532"/>
-      <c r="AY12" s="532"/>
-      <c r="AZ12" s="532"/>
-      <c r="BA12" s="536"/>
-      <c r="BB12" s="536"/>
-      <c r="BC12" s="536"/>
-      <c r="BD12" s="536"/>
-      <c r="BE12" s="536"/>
-      <c r="BF12" s="536"/>
-      <c r="BG12" s="536"/>
-      <c r="BI12" s="532" t="s">
+      <c r="AU12" s="508"/>
+      <c r="AV12" s="508"/>
+      <c r="AW12" s="508"/>
+      <c r="AX12" s="508"/>
+      <c r="AY12" s="508"/>
+      <c r="AZ12" s="508"/>
+      <c r="BA12" s="538"/>
+      <c r="BB12" s="538"/>
+      <c r="BC12" s="538"/>
+      <c r="BD12" s="538"/>
+      <c r="BE12" s="538"/>
+      <c r="BF12" s="538"/>
+      <c r="BG12" s="538"/>
+      <c r="BI12" s="508" t="s">
         <v>293</v>
       </c>
-      <c r="BJ12" s="532"/>
-      <c r="BK12" s="532"/>
-      <c r="BL12" s="532"/>
-      <c r="BM12" s="532"/>
-      <c r="BN12" s="532"/>
-      <c r="BX12" s="537" t="s">
+      <c r="BJ12" s="508"/>
+      <c r="BK12" s="508"/>
+      <c r="BL12" s="508"/>
+      <c r="BM12" s="508"/>
+      <c r="BN12" s="508"/>
+      <c r="BX12" s="539" t="s">
         <v>294</v>
       </c>
-      <c r="BY12" s="537"/>
-      <c r="BZ12" s="537"/>
-      <c r="CA12" s="537"/>
-      <c r="CB12" s="537"/>
-      <c r="CC12" s="537"/>
+      <c r="BY12" s="539"/>
+      <c r="BZ12" s="539"/>
+      <c r="CA12" s="539"/>
+      <c r="CB12" s="539"/>
+      <c r="CC12" s="539"/>
     </row>
     <row r="13" spans="1:89 16342:16384" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A13" s="136">
@@ -13482,102 +13496,102 @@
       <c r="XFD18" s="3"/>
     </row>
     <row r="19" spans="1:89 16342:16384" s="1" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="509" t="s">
+      <c r="A19" s="540" t="s">
         <v>323</v>
       </c>
-      <c r="B19" s="510"/>
-      <c r="C19" s="510"/>
-      <c r="D19" s="510"/>
-      <c r="E19" s="510"/>
-      <c r="F19" s="510"/>
-      <c r="G19" s="510"/>
-      <c r="H19" s="510"/>
-      <c r="I19" s="510"/>
-      <c r="J19" s="510"/>
-      <c r="K19" s="510"/>
-      <c r="L19" s="510"/>
-      <c r="M19" s="510"/>
-      <c r="N19" s="510"/>
-      <c r="P19" s="538" t="s">
+      <c r="B19" s="541"/>
+      <c r="C19" s="541"/>
+      <c r="D19" s="541"/>
+      <c r="E19" s="541"/>
+      <c r="F19" s="541"/>
+      <c r="G19" s="541"/>
+      <c r="H19" s="541"/>
+      <c r="I19" s="541"/>
+      <c r="J19" s="541"/>
+      <c r="K19" s="541"/>
+      <c r="L19" s="541"/>
+      <c r="M19" s="541"/>
+      <c r="N19" s="541"/>
+      <c r="P19" s="542" t="s">
         <v>324</v>
       </c>
-      <c r="Q19" s="539"/>
-      <c r="R19" s="539"/>
-      <c r="S19" s="539"/>
-      <c r="T19" s="539"/>
-      <c r="U19" s="539"/>
-      <c r="V19" s="539"/>
-      <c r="W19" s="539"/>
-      <c r="X19" s="539"/>
-      <c r="Y19" s="539"/>
-      <c r="Z19" s="539"/>
-      <c r="AA19" s="539"/>
-      <c r="AB19" s="539"/>
-      <c r="AC19" s="539"/>
-      <c r="AE19" s="511" t="s">
+      <c r="Q19" s="543"/>
+      <c r="R19" s="543"/>
+      <c r="S19" s="543"/>
+      <c r="T19" s="543"/>
+      <c r="U19" s="543"/>
+      <c r="V19" s="543"/>
+      <c r="W19" s="543"/>
+      <c r="X19" s="543"/>
+      <c r="Y19" s="543"/>
+      <c r="Z19" s="543"/>
+      <c r="AA19" s="543"/>
+      <c r="AB19" s="543"/>
+      <c r="AC19" s="543"/>
+      <c r="AE19" s="544" t="s">
         <v>325</v>
       </c>
-      <c r="AF19" s="512"/>
-      <c r="AG19" s="512"/>
-      <c r="AH19" s="512"/>
-      <c r="AI19" s="512"/>
-      <c r="AJ19" s="512"/>
-      <c r="AK19" s="512"/>
-      <c r="AL19" s="512"/>
-      <c r="AM19" s="512"/>
-      <c r="AN19" s="512"/>
-      <c r="AO19" s="512"/>
-      <c r="AP19" s="512"/>
-      <c r="AQ19" s="512"/>
-      <c r="AR19" s="512"/>
-      <c r="AT19" s="538" t="s">
+      <c r="AF19" s="545"/>
+      <c r="AG19" s="545"/>
+      <c r="AH19" s="545"/>
+      <c r="AI19" s="545"/>
+      <c r="AJ19" s="545"/>
+      <c r="AK19" s="545"/>
+      <c r="AL19" s="545"/>
+      <c r="AM19" s="545"/>
+      <c r="AN19" s="545"/>
+      <c r="AO19" s="545"/>
+      <c r="AP19" s="545"/>
+      <c r="AQ19" s="545"/>
+      <c r="AR19" s="545"/>
+      <c r="AT19" s="542" t="s">
         <v>326</v>
       </c>
-      <c r="AU19" s="538"/>
-      <c r="AV19" s="538"/>
-      <c r="AW19" s="538"/>
-      <c r="AX19" s="538"/>
-      <c r="AY19" s="538"/>
-      <c r="AZ19" s="538"/>
-      <c r="BA19" s="538"/>
-      <c r="BB19" s="538"/>
-      <c r="BC19" s="538"/>
-      <c r="BD19" s="538"/>
-      <c r="BE19" s="538"/>
-      <c r="BF19" s="538"/>
-      <c r="BG19" s="538"/>
-      <c r="BI19" s="509" t="s">
+      <c r="AU19" s="542"/>
+      <c r="AV19" s="542"/>
+      <c r="AW19" s="542"/>
+      <c r="AX19" s="542"/>
+      <c r="AY19" s="542"/>
+      <c r="AZ19" s="542"/>
+      <c r="BA19" s="542"/>
+      <c r="BB19" s="542"/>
+      <c r="BC19" s="542"/>
+      <c r="BD19" s="542"/>
+      <c r="BE19" s="542"/>
+      <c r="BF19" s="542"/>
+      <c r="BG19" s="542"/>
+      <c r="BI19" s="540" t="s">
         <v>327</v>
       </c>
-      <c r="BJ19" s="510"/>
-      <c r="BK19" s="510"/>
-      <c r="BL19" s="510"/>
-      <c r="BM19" s="510"/>
-      <c r="BN19" s="510"/>
-      <c r="BO19" s="510"/>
-      <c r="BP19" s="510"/>
-      <c r="BQ19" s="510"/>
-      <c r="BR19" s="510"/>
-      <c r="BS19" s="510"/>
-      <c r="BT19" s="510"/>
-      <c r="BU19" s="510"/>
-      <c r="BV19" s="510"/>
-      <c r="BX19" s="509" t="s">
+      <c r="BJ19" s="541"/>
+      <c r="BK19" s="541"/>
+      <c r="BL19" s="541"/>
+      <c r="BM19" s="541"/>
+      <c r="BN19" s="541"/>
+      <c r="BO19" s="541"/>
+      <c r="BP19" s="541"/>
+      <c r="BQ19" s="541"/>
+      <c r="BR19" s="541"/>
+      <c r="BS19" s="541"/>
+      <c r="BT19" s="541"/>
+      <c r="BU19" s="541"/>
+      <c r="BV19" s="541"/>
+      <c r="BX19" s="540" t="s">
         <v>328</v>
       </c>
-      <c r="BY19" s="510"/>
-      <c r="BZ19" s="510"/>
-      <c r="CA19" s="510"/>
-      <c r="CB19" s="510"/>
-      <c r="CC19" s="510"/>
-      <c r="CD19" s="510"/>
-      <c r="CE19" s="510"/>
-      <c r="CF19" s="510"/>
-      <c r="CG19" s="510"/>
-      <c r="CH19" s="510"/>
-      <c r="CI19" s="510"/>
-      <c r="CJ19" s="510"/>
-      <c r="CK19" s="510"/>
+      <c r="BY19" s="541"/>
+      <c r="BZ19" s="541"/>
+      <c r="CA19" s="541"/>
+      <c r="CB19" s="541"/>
+      <c r="CC19" s="541"/>
+      <c r="CD19" s="541"/>
+      <c r="CE19" s="541"/>
+      <c r="CF19" s="541"/>
+      <c r="CG19" s="541"/>
+      <c r="CH19" s="541"/>
+      <c r="CI19" s="541"/>
+      <c r="CJ19" s="541"/>
+      <c r="CK19" s="541"/>
       <c r="XDN19" s="3"/>
       <c r="XDO19" s="3"/>
       <c r="XDP19" s="3"/>
@@ -13623,174 +13637,174 @@
       <c r="XFD19" s="3"/>
     </row>
     <row r="20" spans="1:89 16342:16384" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="A20" s="513" t="s">
+      <c r="A20" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="B20" s="514"/>
-      <c r="C20" s="513" t="s">
+      <c r="B20" s="530"/>
+      <c r="C20" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="515"/>
-      <c r="E20" s="513" t="s">
+      <c r="D20" s="526"/>
+      <c r="E20" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="516"/>
-      <c r="G20" s="513" t="s">
+      <c r="F20" s="527"/>
+      <c r="G20" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="515"/>
-      <c r="I20" s="513" t="s">
+      <c r="H20" s="526"/>
+      <c r="I20" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="515"/>
-      <c r="K20" s="517" t="s">
+      <c r="J20" s="526"/>
+      <c r="K20" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="518"/>
-      <c r="M20" s="513" t="s">
+      <c r="L20" s="529"/>
+      <c r="M20" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="514"/>
-      <c r="P20" s="513" t="s">
+      <c r="N20" s="530"/>
+      <c r="P20" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="Q20" s="514"/>
-      <c r="R20" s="513" t="s">
+      <c r="Q20" s="530"/>
+      <c r="R20" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="515"/>
-      <c r="T20" s="513" t="s">
+      <c r="S20" s="526"/>
+      <c r="T20" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="U20" s="516"/>
-      <c r="V20" s="513" t="s">
+      <c r="U20" s="527"/>
+      <c r="V20" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="W20" s="515"/>
-      <c r="X20" s="513" t="s">
+      <c r="W20" s="526"/>
+      <c r="X20" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="Y20" s="515"/>
-      <c r="Z20" s="517" t="s">
+      <c r="Y20" s="526"/>
+      <c r="Z20" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="AA20" s="518"/>
-      <c r="AB20" s="513" t="s">
+      <c r="AA20" s="529"/>
+      <c r="AB20" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="AC20" s="514"/>
-      <c r="AE20" s="513" t="s">
+      <c r="AC20" s="530"/>
+      <c r="AE20" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="AF20" s="514"/>
-      <c r="AG20" s="513" t="s">
+      <c r="AF20" s="530"/>
+      <c r="AG20" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="AH20" s="515"/>
-      <c r="AI20" s="513" t="s">
+      <c r="AH20" s="526"/>
+      <c r="AI20" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="AJ20" s="516"/>
-      <c r="AK20" s="513" t="s">
+      <c r="AJ20" s="527"/>
+      <c r="AK20" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="AL20" s="515"/>
-      <c r="AM20" s="513" t="s">
+      <c r="AL20" s="526"/>
+      <c r="AM20" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="AN20" s="515"/>
-      <c r="AO20" s="517" t="s">
+      <c r="AN20" s="526"/>
+      <c r="AO20" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="AP20" s="518"/>
-      <c r="AQ20" s="513" t="s">
+      <c r="AP20" s="529"/>
+      <c r="AQ20" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="AR20" s="514"/>
-      <c r="AT20" s="513" t="s">
+      <c r="AR20" s="530"/>
+      <c r="AT20" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="AU20" s="514"/>
-      <c r="AV20" s="513" t="s">
+      <c r="AU20" s="530"/>
+      <c r="AV20" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="AW20" s="513"/>
-      <c r="AX20" s="513" t="s">
+      <c r="AW20" s="525"/>
+      <c r="AX20" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="AY20" s="516"/>
-      <c r="AZ20" s="513" t="s">
+      <c r="AY20" s="527"/>
+      <c r="AZ20" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="BA20" s="515"/>
-      <c r="BB20" s="513" t="s">
+      <c r="BA20" s="526"/>
+      <c r="BB20" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="BC20" s="515"/>
-      <c r="BD20" s="517" t="s">
+      <c r="BC20" s="526"/>
+      <c r="BD20" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="BE20" s="518"/>
-      <c r="BF20" s="513" t="s">
+      <c r="BE20" s="529"/>
+      <c r="BF20" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="BG20" s="514"/>
-      <c r="BI20" s="513" t="s">
+      <c r="BG20" s="530"/>
+      <c r="BI20" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="BJ20" s="514"/>
-      <c r="BK20" s="513" t="s">
+      <c r="BJ20" s="530"/>
+      <c r="BK20" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="BL20" s="515"/>
-      <c r="BM20" s="513" t="s">
+      <c r="BL20" s="526"/>
+      <c r="BM20" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="BN20" s="516"/>
-      <c r="BO20" s="513" t="s">
+      <c r="BN20" s="527"/>
+      <c r="BO20" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="BP20" s="515"/>
-      <c r="BQ20" s="513" t="s">
+      <c r="BP20" s="526"/>
+      <c r="BQ20" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="BR20" s="515"/>
-      <c r="BS20" s="517" t="s">
+      <c r="BR20" s="526"/>
+      <c r="BS20" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="BT20" s="518"/>
-      <c r="BU20" s="513" t="s">
+      <c r="BT20" s="529"/>
+      <c r="BU20" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="BV20" s="514"/>
-      <c r="BX20" s="513" t="s">
+      <c r="BV20" s="530"/>
+      <c r="BX20" s="525" t="s">
         <v>281</v>
       </c>
-      <c r="BY20" s="514"/>
-      <c r="BZ20" s="513" t="s">
+      <c r="BY20" s="530"/>
+      <c r="BZ20" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="CA20" s="515"/>
-      <c r="CB20" s="513" t="s">
+      <c r="CA20" s="526"/>
+      <c r="CB20" s="525" t="s">
         <v>4</v>
       </c>
-      <c r="CC20" s="516"/>
-      <c r="CD20" s="513" t="s">
+      <c r="CC20" s="527"/>
+      <c r="CD20" s="525" t="s">
         <v>5</v>
       </c>
-      <c r="CE20" s="515"/>
-      <c r="CF20" s="513" t="s">
+      <c r="CE20" s="526"/>
+      <c r="CF20" s="525" t="s">
         <v>6</v>
       </c>
-      <c r="CG20" s="515"/>
-      <c r="CH20" s="517" t="s">
+      <c r="CG20" s="526"/>
+      <c r="CH20" s="528" t="s">
         <v>7</v>
       </c>
-      <c r="CI20" s="518"/>
-      <c r="CJ20" s="513" t="s">
+      <c r="CI20" s="529"/>
+      <c r="CJ20" s="525" t="s">
         <v>8</v>
       </c>
-      <c r="CK20" s="514"/>
+      <c r="CK20" s="530"/>
       <c r="XDN20" s="3"/>
       <c r="XDO20" s="3"/>
       <c r="XDP20" s="3"/>
@@ -13836,12 +13850,12 @@
       <c r="XFD20" s="3"/>
     </row>
     <row r="21" spans="1:89 16342:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A21" s="524"/>
-      <c r="B21" s="527"/>
-      <c r="C21" s="521"/>
-      <c r="D21" s="523"/>
-      <c r="E21" s="524"/>
-      <c r="F21" s="527"/>
+      <c r="A21" s="531"/>
+      <c r="B21" s="532"/>
+      <c r="C21" s="533"/>
+      <c r="D21" s="534"/>
+      <c r="E21" s="531"/>
+      <c r="F21" s="532"/>
       <c r="G21" s="5"/>
       <c r="H21" s="6"/>
       <c r="I21" s="5"/>
@@ -15082,22 +15096,22 @@
       <c r="AP25" s="103"/>
       <c r="AQ25" s="5"/>
       <c r="AR25" s="6"/>
-      <c r="AT25" s="543" t="s">
+      <c r="AT25" s="512" t="s">
         <v>282</v>
       </c>
-      <c r="AU25" s="544"/>
-      <c r="AV25" s="544"/>
-      <c r="AW25" s="544"/>
-      <c r="AX25" s="544"/>
-      <c r="AY25" s="544"/>
-      <c r="AZ25" s="544"/>
-      <c r="BA25" s="544"/>
-      <c r="BB25" s="544"/>
-      <c r="BC25" s="544"/>
-      <c r="BD25" s="544"/>
-      <c r="BE25" s="544"/>
-      <c r="BF25" s="544"/>
-      <c r="BG25" s="545"/>
+      <c r="AU25" s="513"/>
+      <c r="AV25" s="513"/>
+      <c r="AW25" s="513"/>
+      <c r="AX25" s="513"/>
+      <c r="AY25" s="513"/>
+      <c r="AZ25" s="513"/>
+      <c r="BA25" s="513"/>
+      <c r="BB25" s="513"/>
+      <c r="BC25" s="513"/>
+      <c r="BD25" s="513"/>
+      <c r="BE25" s="513"/>
+      <c r="BF25" s="513"/>
+      <c r="BG25" s="514"/>
       <c r="BI25" s="240">
         <v>26</v>
       </c>
@@ -15221,64 +15235,64 @@
       <c r="L26" s="243"/>
       <c r="M26" s="15"/>
       <c r="N26" s="246"/>
-      <c r="P26" s="546" t="s">
+      <c r="P26" s="515" t="s">
         <v>287</v>
       </c>
-      <c r="Q26" s="547"/>
-      <c r="R26" s="547"/>
-      <c r="S26" s="547"/>
-      <c r="T26" s="547"/>
-      <c r="U26" s="547"/>
-      <c r="V26" s="547"/>
-      <c r="W26" s="547"/>
-      <c r="X26" s="547"/>
-      <c r="Y26" s="547"/>
-      <c r="Z26" s="547"/>
-      <c r="AA26" s="547"/>
-      <c r="AB26" s="547"/>
-      <c r="AC26" s="547"/>
-      <c r="AD26" s="548"/>
-      <c r="AE26" s="530" t="s">
+      <c r="Q26" s="516"/>
+      <c r="R26" s="516"/>
+      <c r="S26" s="516"/>
+      <c r="T26" s="516"/>
+      <c r="U26" s="516"/>
+      <c r="V26" s="516"/>
+      <c r="W26" s="516"/>
+      <c r="X26" s="516"/>
+      <c r="Y26" s="516"/>
+      <c r="Z26" s="516"/>
+      <c r="AA26" s="516"/>
+      <c r="AB26" s="516"/>
+      <c r="AC26" s="516"/>
+      <c r="AD26" s="517"/>
+      <c r="AE26" s="518" t="s">
         <v>329</v>
       </c>
-      <c r="AF26" s="530"/>
-      <c r="AG26" s="530"/>
-      <c r="AH26" s="530"/>
-      <c r="AI26" s="530"/>
-      <c r="AJ26" s="530"/>
-      <c r="AK26" s="530"/>
-      <c r="AL26" s="530"/>
-      <c r="AM26" s="530"/>
-      <c r="AN26" s="530"/>
-      <c r="AO26" s="530"/>
-      <c r="AP26" s="530"/>
-      <c r="AQ26" s="530"/>
-      <c r="AR26" s="530"/>
-      <c r="AT26" s="549" t="s">
+      <c r="AF26" s="518"/>
+      <c r="AG26" s="518"/>
+      <c r="AH26" s="518"/>
+      <c r="AI26" s="518"/>
+      <c r="AJ26" s="518"/>
+      <c r="AK26" s="518"/>
+      <c r="AL26" s="518"/>
+      <c r="AM26" s="518"/>
+      <c r="AN26" s="518"/>
+      <c r="AO26" s="518"/>
+      <c r="AP26" s="518"/>
+      <c r="AQ26" s="518"/>
+      <c r="AR26" s="518"/>
+      <c r="AT26" s="519" t="s">
         <v>330</v>
       </c>
-      <c r="AU26" s="549"/>
-      <c r="AV26" s="549"/>
-      <c r="AW26" s="549"/>
-      <c r="AX26" s="549"/>
-      <c r="AY26" s="549"/>
-      <c r="AZ26" s="549"/>
-      <c r="BI26" s="550" t="s">
+      <c r="AU26" s="519"/>
+      <c r="AV26" s="519"/>
+      <c r="AW26" s="519"/>
+      <c r="AX26" s="519"/>
+      <c r="AY26" s="519"/>
+      <c r="AZ26" s="519"/>
+      <c r="BI26" s="520" t="s">
         <v>287</v>
       </c>
-      <c r="BJ26" s="551"/>
-      <c r="BK26" s="551"/>
-      <c r="BL26" s="551"/>
-      <c r="BM26" s="551"/>
-      <c r="BN26" s="551"/>
-      <c r="BO26" s="551"/>
-      <c r="BP26" s="551"/>
-      <c r="BQ26" s="551"/>
-      <c r="BR26" s="551"/>
-      <c r="BS26" s="551"/>
-      <c r="BT26" s="551"/>
-      <c r="BU26" s="551"/>
-      <c r="BV26" s="552"/>
+      <c r="BJ26" s="521"/>
+      <c r="BK26" s="521"/>
+      <c r="BL26" s="521"/>
+      <c r="BM26" s="521"/>
+      <c r="BN26" s="521"/>
+      <c r="BO26" s="521"/>
+      <c r="BP26" s="521"/>
+      <c r="BQ26" s="521"/>
+      <c r="BR26" s="521"/>
+      <c r="BS26" s="521"/>
+      <c r="BT26" s="521"/>
+      <c r="BU26" s="521"/>
+      <c r="BV26" s="522"/>
       <c r="BX26" s="15"/>
       <c r="BY26" s="243"/>
       <c r="BZ26" s="15"/>
@@ -15338,32 +15352,32 @@
       <c r="XFD26" s="3"/>
     </row>
     <row r="27" spans="1:89 16342:16384" s="1" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="A27" s="553" t="s">
+      <c r="A27" s="523" t="s">
         <v>282</v>
       </c>
-      <c r="B27" s="553"/>
-      <c r="C27" s="553"/>
-      <c r="D27" s="553"/>
-      <c r="E27" s="553"/>
-      <c r="F27" s="553"/>
-      <c r="G27" s="553"/>
-      <c r="H27" s="553"/>
-      <c r="I27" s="553"/>
-      <c r="J27" s="553"/>
-      <c r="K27" s="553"/>
-      <c r="L27" s="553"/>
-      <c r="M27" s="553"/>
-      <c r="N27" s="553"/>
-      <c r="AE27" s="532" t="s">
+      <c r="B27" s="523"/>
+      <c r="C27" s="523"/>
+      <c r="D27" s="523"/>
+      <c r="E27" s="523"/>
+      <c r="F27" s="523"/>
+      <c r="G27" s="523"/>
+      <c r="H27" s="523"/>
+      <c r="I27" s="523"/>
+      <c r="J27" s="523"/>
+      <c r="K27" s="523"/>
+      <c r="L27" s="523"/>
+      <c r="M27" s="523"/>
+      <c r="N27" s="523"/>
+      <c r="AE27" s="508" t="s">
         <v>331</v>
       </c>
-      <c r="AF27" s="532"/>
-      <c r="AG27" s="532"/>
-      <c r="AH27" s="532"/>
-      <c r="AI27" s="532"/>
-      <c r="AJ27" s="532"/>
-      <c r="AK27" s="532"/>
-      <c r="AL27" s="532"/>
+      <c r="AF27" s="508"/>
+      <c r="AG27" s="508"/>
+      <c r="AH27" s="508"/>
+      <c r="AI27" s="508"/>
+      <c r="AJ27" s="508"/>
+      <c r="AK27" s="508"/>
+      <c r="AL27" s="508"/>
       <c r="AM27" s="129"/>
       <c r="AN27" s="248"/>
       <c r="AO27" s="248"/>
@@ -15377,30 +15391,30 @@
         <v>333</v>
       </c>
       <c r="AV27" s="2"/>
-      <c r="BI27" s="554" t="s">
+      <c r="BI27" s="524" t="s">
         <v>334</v>
       </c>
-      <c r="BJ27" s="554"/>
-      <c r="BK27" s="554"/>
-      <c r="BL27" s="554"/>
-      <c r="BM27" s="554"/>
-      <c r="BN27" s="554"/>
-      <c r="BX27" s="530" t="s">
+      <c r="BJ27" s="524"/>
+      <c r="BK27" s="524"/>
+      <c r="BL27" s="524"/>
+      <c r="BM27" s="524"/>
+      <c r="BN27" s="524"/>
+      <c r="BX27" s="518" t="s">
         <v>329</v>
       </c>
-      <c r="BY27" s="530"/>
-      <c r="BZ27" s="530"/>
-      <c r="CA27" s="530"/>
-      <c r="CB27" s="530"/>
-      <c r="CC27" s="530"/>
-      <c r="CD27" s="530"/>
-      <c r="CE27" s="530"/>
-      <c r="CF27" s="530"/>
-      <c r="CG27" s="530"/>
-      <c r="CH27" s="530"/>
-      <c r="CI27" s="530"/>
-      <c r="CJ27" s="530"/>
-      <c r="CK27" s="530"/>
+      <c r="BY27" s="518"/>
+      <c r="BZ27" s="518"/>
+      <c r="CA27" s="518"/>
+      <c r="CB27" s="518"/>
+      <c r="CC27" s="518"/>
+      <c r="CD27" s="518"/>
+      <c r="CE27" s="518"/>
+      <c r="CF27" s="518"/>
+      <c r="CG27" s="518"/>
+      <c r="CH27" s="518"/>
+      <c r="CI27" s="518"/>
+      <c r="CJ27" s="518"/>
+      <c r="CK27" s="518"/>
       <c r="XDN27" s="3"/>
       <c r="XDO27" s="3"/>
       <c r="XDP27" s="3"/>
@@ -15446,31 +15460,31 @@
       <c r="XFD27" s="3"/>
     </row>
     <row r="28" spans="1:89 16342:16384" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A28" s="532" t="s">
+      <c r="A28" s="508" t="s">
         <v>335</v>
       </c>
-      <c r="B28" s="532"/>
-      <c r="C28" s="532"/>
-      <c r="D28" s="532"/>
-      <c r="E28" s="532"/>
-      <c r="F28" s="532"/>
-      <c r="G28" s="532"/>
-      <c r="P28" s="532" t="s">
+      <c r="B28" s="508"/>
+      <c r="C28" s="508"/>
+      <c r="D28" s="508"/>
+      <c r="E28" s="508"/>
+      <c r="F28" s="508"/>
+      <c r="G28" s="508"/>
+      <c r="P28" s="508" t="s">
         <v>336</v>
       </c>
-      <c r="Q28" s="532"/>
-      <c r="R28" s="532"/>
-      <c r="S28" s="532"/>
-      <c r="T28" s="532"/>
-      <c r="U28" s="532"/>
-      <c r="V28" s="532"/>
+      <c r="Q28" s="508"/>
+      <c r="R28" s="508"/>
+      <c r="S28" s="508"/>
+      <c r="T28" s="508"/>
+      <c r="U28" s="508"/>
+      <c r="V28" s="508"/>
       <c r="W28" s="128"/>
       <c r="X28" s="128"/>
-      <c r="Y28" s="540"/>
-      <c r="Z28" s="540"/>
-      <c r="AA28" s="540"/>
-      <c r="AB28" s="540"/>
-      <c r="AC28" s="540"/>
+      <c r="Y28" s="509"/>
+      <c r="Z28" s="509"/>
+      <c r="AA28" s="509"/>
+      <c r="AB28" s="509"/>
+      <c r="AC28" s="509"/>
       <c r="AE28" s="21">
         <v>6</v>
       </c>
@@ -15496,15 +15510,15 @@
       <c r="BJ28" s="150" t="s">
         <v>299</v>
       </c>
-      <c r="BX28" s="541" t="s">
+      <c r="BX28" s="510" t="s">
         <v>339</v>
       </c>
-      <c r="BY28" s="541"/>
-      <c r="BZ28" s="541"/>
-      <c r="CA28" s="541"/>
-      <c r="CB28" s="541"/>
-      <c r="CC28" s="541"/>
-      <c r="CD28" s="541"/>
+      <c r="BY28" s="510"/>
+      <c r="BZ28" s="510"/>
+      <c r="CA28" s="510"/>
+      <c r="CB28" s="510"/>
+      <c r="CC28" s="510"/>
+      <c r="CD28" s="510"/>
       <c r="XDN28" s="3"/>
       <c r="XDO28" s="3"/>
       <c r="XDP28" s="3"/>
@@ -15861,13 +15875,13 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="129"/>
-      <c r="H32" s="542"/>
-      <c r="I32" s="542"/>
-      <c r="J32" s="542"/>
-      <c r="K32" s="542"/>
-      <c r="L32" s="542"/>
-      <c r="M32" s="542"/>
-      <c r="N32" s="542"/>
+      <c r="H32" s="511"/>
+      <c r="I32" s="511"/>
+      <c r="J32" s="511"/>
+      <c r="K32" s="511"/>
+      <c r="L32" s="511"/>
+      <c r="M32" s="511"/>
+      <c r="N32" s="511"/>
       <c r="P32" s="21">
         <v>4</v>
       </c>
@@ -18216,20 +18230,121 @@
     <row r="87" spans="1:44" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="153">
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="Y28:AC28"/>
-    <mergeCell ref="BX28:CD28"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="AT25:BG25"/>
-    <mergeCell ref="P26:AD26"/>
-    <mergeCell ref="AE26:AR26"/>
-    <mergeCell ref="AT26:AZ26"/>
-    <mergeCell ref="BI26:BV26"/>
-    <mergeCell ref="A27:N27"/>
-    <mergeCell ref="AE27:AL27"/>
-    <mergeCell ref="BI27:BN27"/>
-    <mergeCell ref="BX27:CK27"/>
+    <mergeCell ref="A1:CK1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="P3:AC3"/>
+    <mergeCell ref="AE3:AR3"/>
+    <mergeCell ref="AT3:BG3"/>
+    <mergeCell ref="BI3:BV3"/>
+    <mergeCell ref="BX3:CK3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="BQ4:BR4"/>
+    <mergeCell ref="BS4:BT4"/>
+    <mergeCell ref="BU4:BV4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AM4:AN4"/>
+    <mergeCell ref="AO4:AP4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="BX4:BY4"/>
+    <mergeCell ref="BZ4:CA4"/>
+    <mergeCell ref="CB4:CC4"/>
+    <mergeCell ref="CD4:CE4"/>
+    <mergeCell ref="CF4:CG4"/>
+    <mergeCell ref="CH4:CI4"/>
+    <mergeCell ref="CJ4:CK4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AG5:AH5"/>
+    <mergeCell ref="AI5:AJ5"/>
+    <mergeCell ref="AK5:AL5"/>
+    <mergeCell ref="AM5:AN5"/>
+    <mergeCell ref="AO5:AP5"/>
+    <mergeCell ref="AT5:AU5"/>
+    <mergeCell ref="AV5:AW5"/>
+    <mergeCell ref="AX5:AY5"/>
+    <mergeCell ref="AZ5:BA5"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BI4:BJ4"/>
+    <mergeCell ref="BK4:BL4"/>
+    <mergeCell ref="BM4:BN4"/>
+    <mergeCell ref="BO4:BP4"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="P10:AC10"/>
+    <mergeCell ref="AG10:AH10"/>
+    <mergeCell ref="AI10:AJ10"/>
+    <mergeCell ref="AK10:AL10"/>
+    <mergeCell ref="AM10:AN10"/>
+    <mergeCell ref="AO10:AP10"/>
+    <mergeCell ref="AQ10:AR10"/>
+    <mergeCell ref="AT10:AU10"/>
+    <mergeCell ref="AV10:AW10"/>
+    <mergeCell ref="AX10:AY10"/>
+    <mergeCell ref="AZ10:BA10"/>
+    <mergeCell ref="BB10:BC10"/>
+    <mergeCell ref="BD10:BE10"/>
+    <mergeCell ref="BF10:BG10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="P11:W11"/>
+    <mergeCell ref="AE11:AR11"/>
+    <mergeCell ref="AT11:BG11"/>
+    <mergeCell ref="BI11:BV11"/>
+    <mergeCell ref="BX11:CK11"/>
+    <mergeCell ref="AE12:AM12"/>
+    <mergeCell ref="AT12:AZ12"/>
+    <mergeCell ref="BA12:BG12"/>
+    <mergeCell ref="BI12:BN12"/>
+    <mergeCell ref="BX12:CC12"/>
+    <mergeCell ref="A19:N19"/>
+    <mergeCell ref="P19:AC19"/>
+    <mergeCell ref="AE19:AR19"/>
+    <mergeCell ref="AT19:BG19"/>
+    <mergeCell ref="BI19:BV19"/>
+    <mergeCell ref="BX19:CK19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="AZ20:BA20"/>
+    <mergeCell ref="BB20:BC20"/>
+    <mergeCell ref="BD20:BE20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="AB20:AC20"/>
+    <mergeCell ref="AE20:AF20"/>
+    <mergeCell ref="AG20:AH20"/>
+    <mergeCell ref="AI20:AJ20"/>
+    <mergeCell ref="AK20:AL20"/>
     <mergeCell ref="BZ20:CA20"/>
     <mergeCell ref="CB20:CC20"/>
     <mergeCell ref="CD20:CE20"/>
@@ -18254,121 +18369,20 @@
     <mergeCell ref="AT20:AU20"/>
     <mergeCell ref="AV20:AW20"/>
     <mergeCell ref="AX20:AY20"/>
-    <mergeCell ref="AZ20:BA20"/>
-    <mergeCell ref="BB20:BC20"/>
-    <mergeCell ref="BD20:BE20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="AB20:AC20"/>
-    <mergeCell ref="AE20:AF20"/>
-    <mergeCell ref="AG20:AH20"/>
-    <mergeCell ref="AI20:AJ20"/>
-    <mergeCell ref="AK20:AL20"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="BI11:BV11"/>
-    <mergeCell ref="BX11:CK11"/>
-    <mergeCell ref="AE12:AM12"/>
-    <mergeCell ref="AT12:AZ12"/>
-    <mergeCell ref="BA12:BG12"/>
-    <mergeCell ref="BI12:BN12"/>
-    <mergeCell ref="BX12:CC12"/>
-    <mergeCell ref="A19:N19"/>
-    <mergeCell ref="P19:AC19"/>
-    <mergeCell ref="AE19:AR19"/>
-    <mergeCell ref="AT19:BG19"/>
-    <mergeCell ref="BI19:BV19"/>
-    <mergeCell ref="BX19:CK19"/>
-    <mergeCell ref="AQ10:AR10"/>
-    <mergeCell ref="AT10:AU10"/>
-    <mergeCell ref="AV10:AW10"/>
-    <mergeCell ref="AX10:AY10"/>
-    <mergeCell ref="AZ10:BA10"/>
-    <mergeCell ref="BB10:BC10"/>
-    <mergeCell ref="BD10:BE10"/>
-    <mergeCell ref="BF10:BG10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="P11:W11"/>
-    <mergeCell ref="AE11:AR11"/>
-    <mergeCell ref="AT11:BG11"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="P10:AC10"/>
-    <mergeCell ref="AG10:AH10"/>
-    <mergeCell ref="AI10:AJ10"/>
-    <mergeCell ref="AK10:AL10"/>
-    <mergeCell ref="AM10:AN10"/>
-    <mergeCell ref="AO10:AP10"/>
-    <mergeCell ref="BX4:BY4"/>
-    <mergeCell ref="BZ4:CA4"/>
-    <mergeCell ref="CB4:CC4"/>
-    <mergeCell ref="CD4:CE4"/>
-    <mergeCell ref="CF4:CG4"/>
-    <mergeCell ref="CH4:CI4"/>
-    <mergeCell ref="CJ4:CK4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="AG5:AH5"/>
-    <mergeCell ref="AI5:AJ5"/>
-    <mergeCell ref="AK5:AL5"/>
-    <mergeCell ref="AM5:AN5"/>
-    <mergeCell ref="AO5:AP5"/>
-    <mergeCell ref="AT5:AU5"/>
-    <mergeCell ref="AV5:AW5"/>
-    <mergeCell ref="AX5:AY5"/>
-    <mergeCell ref="AZ5:BA5"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BI4:BJ4"/>
-    <mergeCell ref="BK4:BL4"/>
-    <mergeCell ref="BM4:BN4"/>
-    <mergeCell ref="BO4:BP4"/>
-    <mergeCell ref="BQ4:BR4"/>
-    <mergeCell ref="BS4:BT4"/>
-    <mergeCell ref="BU4:BV4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AM4:AN4"/>
-    <mergeCell ref="AO4:AP4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="A1:CK1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="P3:AC3"/>
-    <mergeCell ref="AE3:AR3"/>
-    <mergeCell ref="AT3:BG3"/>
-    <mergeCell ref="BI3:BV3"/>
-    <mergeCell ref="BX3:CK3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="Y28:AC28"/>
+    <mergeCell ref="BX28:CD28"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="AT25:BG25"/>
+    <mergeCell ref="P26:AD26"/>
+    <mergeCell ref="AE26:AR26"/>
+    <mergeCell ref="AT26:AZ26"/>
+    <mergeCell ref="BI26:BV26"/>
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="AE27:AL27"/>
+    <mergeCell ref="BI27:BN27"/>
+    <mergeCell ref="BX27:CK27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360"/>
